--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="168">
   <si>
     <t>Materia</t>
   </si>
@@ -4328,13 +4328,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -4343,82 +4343,106 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="P1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4433,13 +4457,13 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4454,21 +4478,39 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4477,48 +4519,66 @@
         <v>100</v>
       </c>
       <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
         <v>95</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
       <c r="G5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
         <v>95</v>
       </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
       <c r="N5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>95</v>
       </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4533,13 +4593,13 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -4554,21 +4614,39 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4583,13 +4661,13 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -4604,21 +4682,39 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4633,13 +4729,13 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -4654,21 +4750,39 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4683,13 +4797,13 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -4704,21 +4818,39 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4733,13 +4865,13 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4754,21 +4886,39 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4777,48 +4927,66 @@
         <v>100</v>
       </c>
       <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
         <v>95</v>
       </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
       <c r="G11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
         <v>95</v>
       </c>
-      <c r="K11">
-        <v>100</v>
-      </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
       <c r="N11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>95</v>
       </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -4833,13 +5001,13 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4854,21 +5022,39 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4883,13 +5069,13 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4904,21 +5090,39 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4933,13 +5137,13 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4954,21 +5158,39 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
+        <v>100</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4977,48 +5199,66 @@
         <v>100</v>
       </c>
       <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15">
         <v>90</v>
       </c>
-      <c r="F15">
-        <v>100</v>
-      </c>
       <c r="G15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
         <v>90</v>
       </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
       <c r="N15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>90</v>
       </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -5033,13 +5273,13 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -5054,21 +5294,39 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -5083,13 +5341,13 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -5104,21 +5362,39 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -5133,13 +5409,13 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -5154,21 +5430,39 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5177,48 +5471,66 @@
         <v>100</v>
       </c>
       <c r="E19">
+        <v>100</v>
+      </c>
+      <c r="F19">
         <v>90</v>
       </c>
-      <c r="F19">
-        <v>100</v>
-      </c>
       <c r="G19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
         <v>90</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
       <c r="N19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>90</v>
       </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5233,13 +5545,13 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -5254,21 +5566,39 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -5283,13 +5613,13 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -5304,21 +5634,39 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5333,13 +5681,13 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -5354,21 +5702,39 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5383,13 +5749,13 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -5404,71 +5770,107 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
         <v>79.2</v>
       </c>
-      <c r="D24">
-        <v>100</v>
-      </c>
       <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
         <v>90</v>
       </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
       <c r="G24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>79.2</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
-      <c r="J24">
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24">
         <v>90</v>
       </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-      <c r="M24">
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>79.2</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
         <v>90</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5477,48 +5879,66 @@
         <v>100</v>
       </c>
       <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
         <v>90</v>
       </c>
-      <c r="F25">
-        <v>100</v>
-      </c>
       <c r="G25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
         <v>90</v>
       </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
       <c r="N25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
         <v>90</v>
       </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5527,48 +5947,66 @@
         <v>100</v>
       </c>
       <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
         <v>90</v>
       </c>
-      <c r="F26">
-        <v>100</v>
-      </c>
       <c r="G26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
         <v>90</v>
       </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
       <c r="N26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>90</v>
       </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5583,13 +6021,13 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5604,21 +6042,39 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5627,48 +6083,66 @@
         <v>100</v>
       </c>
       <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
         <v>50</v>
       </c>
-      <c r="F28">
-        <v>100</v>
-      </c>
       <c r="G28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
         <v>50</v>
       </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
       <c r="N28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>50</v>
       </c>
-      <c r="P28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5683,13 +6157,13 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5704,21 +6178,39 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
+        <v>100</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5733,13 +6225,13 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5754,28 +6246,46 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
         <v>87.5</v>
       </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
       <c r="E31">
         <v>100</v>
       </c>
@@ -5783,42 +6293,60 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
         <v>87.5</v>
       </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>87.5</v>
       </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
-      <c r="P31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>100</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5833,13 +6361,13 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -5854,21 +6382,39 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5883,13 +6429,13 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5904,21 +6450,39 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -5933,13 +6497,13 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>100</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5954,71 +6518,107 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>100</v>
       </c>
       <c r="P34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
         <v>83.3</v>
       </c>
-      <c r="D35">
-        <v>100</v>
-      </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
         <v>83.3</v>
       </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>83.3</v>
       </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6033,13 +6633,13 @@
         <v>100</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -6054,21 +6654,39 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
+        <v>100</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6083,13 +6701,13 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>100</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -6104,21 +6722,39 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>100</v>
       </c>
       <c r="P37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
+        <v>100</v>
+      </c>
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6133,13 +6769,13 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>100</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <v>100</v>
@@ -6154,21 +6790,39 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
+        <v>100</v>
+      </c>
+      <c r="S38">
+        <v>100</v>
+      </c>
+      <c r="T38">
+        <v>100</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6177,48 +6831,66 @@
         <v>100</v>
       </c>
       <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="F39">
         <v>90</v>
       </c>
-      <c r="F39">
-        <v>100</v>
-      </c>
       <c r="G39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J39">
+        <v>100</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>100</v>
+      </c>
+      <c r="M39">
         <v>90</v>
       </c>
-      <c r="K39">
-        <v>100</v>
-      </c>
-      <c r="L39">
-        <v>100</v>
-      </c>
-      <c r="M39">
-        <v>100</v>
-      </c>
       <c r="N39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O39">
+        <v>100</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>90</v>
       </c>
-      <c r="P39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -6233,13 +6905,13 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>100</v>
       </c>
       <c r="I40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -6254,20 +6926,38 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>100</v>
       </c>
       <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>100</v>
+      </c>
+      <c r="R40">
+        <v>100</v>
+      </c>
+      <c r="S40">
+        <v>100</v>
+      </c>
+      <c r="T40">
+        <v>100</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="103">
   <si>
     <t>Materia</t>
   </si>
@@ -209,24 +209,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -245,280 +245,85 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BALCAZAR</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CASANOVA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CORONA</t>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DEL VALLE</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARZA</t>
-  </si>
-  <si>
     <t>IBARRA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PELAYO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>DEL VALLE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>MARIANA JANET</t>
-  </si>
-  <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>LUCIA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>NAYELY</t>
+    <t>JENNYFER ARIANA</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>ALDRICH ARMANDO</t>
   </si>
   <si>
     <t>MARIEL</t>
   </si>
   <si>
-    <t>JOSE MARCOS</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>LUIS PABLO</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
     <t>ARMANDO</t>
   </si>
   <si>
-    <t>JONATHAN URIEL</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
     <t>IVETTE</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>IVAN JESUS</t>
-  </si>
-  <si>
-    <t>DENILSON AARON</t>
-  </si>
-  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>YURI MONSERRAT</t>
-  </si>
-  <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ALDRICH ARMANDO</t>
-  </si>
-  <si>
-    <t>ALEYDA MONSERRAT</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -1027,7 +832,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1042,19 +847,19 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1063,10 +868,10 @@
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1090,7 +895,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1105,10 +910,10 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1116,7 +921,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -1131,19 +936,19 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1152,10 +957,10 @@
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1179,10 +984,10 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1194,10 +999,10 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1205,7 +1010,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1220,19 +1025,19 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1241,10 +1046,10 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1268,7 +1073,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1283,10 +1088,10 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1294,7 +1099,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1309,19 +1114,19 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1330,10 +1135,10 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1357,13 +1162,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1372,10 +1177,10 @@
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1383,7 +1188,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1398,19 +1203,19 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1419,10 +1224,10 @@
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1446,13 +1251,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1461,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1472,7 +1277,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1487,19 +1292,19 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1508,10 +1313,10 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1535,13 +1340,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1550,7 +1355,7 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1561,7 +1366,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -1576,19 +1381,19 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1597,10 +1402,10 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1624,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1639,7 +1444,7 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1650,7 +1455,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1665,19 +1470,19 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1686,10 +1491,10 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1713,10 +1518,10 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1728,7 +1533,7 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -1739,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1754,19 +1559,19 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1775,10 +1580,10 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1802,13 +1607,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1817,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1828,7 +1633,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1843,19 +1648,19 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1864,10 +1669,10 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1891,10 +1696,10 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1906,10 +1711,10 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1917,7 +1722,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1932,19 +1737,19 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H14">
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1953,10 +1758,10 @@
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1980,13 +1785,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1995,7 +1800,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -2006,7 +1811,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -2021,19 +1826,19 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -2042,10 +1847,10 @@
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2069,10 +1874,10 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -2084,7 +1889,7 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2095,7 +1900,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -2110,19 +1915,19 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2131,10 +1936,10 @@
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2158,13 +1963,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2173,7 +1978,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -2184,7 +1989,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -2199,19 +2004,19 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2220,10 +2025,10 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2247,13 +2052,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -2262,7 +2067,7 @@
         <v>6</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2273,7 +2078,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>7</v>
@@ -2288,19 +2093,19 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H18">
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2309,10 +2114,10 @@
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2336,10 +2141,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2351,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2362,7 +2167,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -2377,19 +2182,19 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2398,10 +2203,10 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2425,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2440,10 +2245,10 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2451,7 +2256,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2466,19 +2271,19 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2487,10 +2292,10 @@
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2514,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2529,7 +2334,7 @@
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2540,7 +2345,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>7</v>
@@ -2555,19 +2360,19 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2576,10 +2381,10 @@
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2603,7 +2408,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2618,10 +2423,10 @@
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2629,7 +2434,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -2644,19 +2449,19 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2665,10 +2470,10 @@
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2692,10 +2497,10 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2707,10 +2512,10 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2718,7 +2523,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -2733,19 +2538,19 @@
         <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2754,10 +2559,10 @@
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2781,10 +2586,10 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2796,10 +2601,10 @@
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2807,7 +2612,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2822,19 +2627,19 @@
         <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2843,10 +2648,10 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2870,10 +2675,10 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2885,7 +2690,7 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -2896,7 +2701,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -2911,19 +2716,19 @@
         <v>5</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2932,10 +2737,10 @@
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2959,7 +2764,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2974,7 +2779,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2985,7 +2790,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>8</v>
@@ -3000,19 +2805,19 @@
         <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H26">
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -3021,10 +2826,10 @@
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -3048,7 +2853,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -3063,10 +2868,10 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3074,7 +2879,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -3089,19 +2894,19 @@
         <v>5</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -3110,10 +2915,10 @@
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3137,13 +2942,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3152,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC27">
         <v>5</v>
@@ -3163,7 +2968,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -3178,19 +2983,19 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -3199,10 +3004,10 @@
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3226,7 +3031,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -3241,7 +3046,7 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>5</v>
@@ -3252,7 +3057,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -3267,19 +3072,19 @@
         <v>5</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3288,10 +3093,10 @@
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3315,13 +3120,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>5</v>
@@ -3330,10 +3135,10 @@
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3341,7 +3146,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -3356,19 +3161,19 @@
         <v>5</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H30">
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3377,10 +3182,10 @@
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3404,7 +3209,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3419,7 +3224,7 @@
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3430,7 +3235,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -3445,19 +3250,19 @@
         <v>6</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3466,10 +3271,10 @@
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3493,13 +3298,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3508,10 +3313,10 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3519,7 +3324,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -3534,19 +3339,19 @@
         <v>6</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3555,10 +3360,10 @@
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3582,13 +3387,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>7</v>
@@ -3597,7 +3402,7 @@
         <v>6</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3608,7 +3413,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -3623,19 +3428,19 @@
         <v>8</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3644,10 +3449,10 @@
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3671,13 +3476,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -3686,7 +3491,7 @@
         <v>8</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3697,7 +3502,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -3712,19 +3517,19 @@
         <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3733,10 +3538,10 @@
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3760,10 +3565,10 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3775,10 +3580,10 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC34">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3786,7 +3591,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>7</v>
@@ -3801,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>5</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3822,10 +3627,10 @@
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3849,7 +3654,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3864,7 +3669,7 @@
         <v>5</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC35">
         <v>5</v>
@@ -3875,7 +3680,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>7</v>
@@ -3890,19 +3695,19 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H36">
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3911,10 +3716,10 @@
         <v>-1</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3938,7 +3743,7 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3953,10 +3758,10 @@
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3964,7 +3769,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -3979,19 +3784,19 @@
         <v>6</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -4000,10 +3805,10 @@
         <v>-1</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -4027,7 +3832,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>5</v>
@@ -4042,7 +3847,7 @@
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC37">
         <v>5</v>
@@ -4053,7 +3858,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>8</v>
@@ -4068,19 +3873,19 @@
         <v>5</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -4089,10 +3894,10 @@
         <v>-1</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4116,10 +3921,10 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -4131,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="AB38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -4142,7 +3947,7 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>8</v>
@@ -4157,19 +3962,19 @@
         <v>5</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H39">
         <v>5</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>-1</v>
@@ -4178,10 +3983,10 @@
         <v>-1</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4205,13 +4010,13 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z39">
         <v>5</v>
@@ -4220,7 +4025,7 @@
         <v>5</v>
       </c>
       <c r="AB39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>5</v>
@@ -4231,7 +4036,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C40">
         <v>8</v>
@@ -4246,19 +4051,19 @@
         <v>6</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H40">
         <v>5</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -4267,10 +4072,10 @@
         <v>-1</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4294,10 +4099,10 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -4309,7 +4114,7 @@
         <v>6</v>
       </c>
       <c r="AB40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC40">
         <v>5</v>
@@ -4442,7 +4247,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4457,13 +4262,13 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4478,13 +4283,13 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4499,7 +4304,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4510,7 +4315,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4525,19 +4330,19 @@
         <v>95</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4546,19 +4351,19 @@
         <v>95</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4567,7 +4372,7 @@
         <v>95</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4578,7 +4383,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4593,19 +4398,19 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4614,19 +4419,19 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4635,7 +4440,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4646,7 +4451,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4661,19 +4466,19 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4682,19 +4487,19 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4703,10 +4508,10 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V7">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4714,7 +4519,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4729,19 +4534,19 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4750,19 +4555,19 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4771,7 +4576,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4782,7 +4587,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4797,19 +4602,19 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -4818,19 +4623,19 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4839,7 +4644,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -4850,7 +4655,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4865,19 +4670,19 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4886,19 +4691,19 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4907,10 +4712,10 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V10">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4918,7 +4723,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4933,19 +4738,19 @@
         <v>95</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4954,19 +4759,19 @@
         <v>95</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4975,7 +4780,7 @@
         <v>95</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4986,7 +4791,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -5001,19 +4806,19 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -5022,19 +4827,19 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -5043,7 +4848,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -5054,7 +4859,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -5069,19 +4874,19 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -5090,19 +4895,19 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -5111,7 +4916,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -5122,7 +4927,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -5137,19 +4942,19 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -5158,19 +4963,19 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -5179,7 +4984,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -5190,7 +4995,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -5205,19 +5010,19 @@
         <v>90</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -5226,19 +5031,19 @@
         <v>90</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5247,7 +5052,7 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -5258,7 +5063,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -5273,19 +5078,19 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -5294,19 +5099,19 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -5315,7 +5120,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5326,7 +5131,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -5341,19 +5146,19 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5362,19 +5167,19 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5383,7 +5188,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5394,7 +5199,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -5409,19 +5214,19 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -5430,19 +5235,19 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5451,7 +5256,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5462,7 +5267,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5477,19 +5282,19 @@
         <v>90</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5498,19 +5303,19 @@
         <v>90</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5519,7 +5324,7 @@
         <v>90</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5530,7 +5335,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5545,19 +5350,19 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5566,19 +5371,19 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5587,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5598,7 +5403,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -5613,19 +5418,19 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5634,19 +5439,19 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5655,7 +5460,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5666,7 +5471,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5681,19 +5486,19 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5702,19 +5507,19 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5723,7 +5528,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5734,7 +5539,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5749,19 +5554,19 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5770,19 +5575,19 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5791,7 +5596,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5802,7 +5607,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -5817,19 +5622,19 @@
         <v>90</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="K24">
-        <v>79.2</v>
+        <v>43.2</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5838,19 +5643,19 @@
         <v>90</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="R24">
-        <v>79.2</v>
+        <v>43.2</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5859,10 +5664,10 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5870,7 +5675,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5885,19 +5690,19 @@
         <v>90</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5906,19 +5711,19 @@
         <v>90</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5927,7 +5732,7 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5938,7 +5743,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5953,19 +5758,19 @@
         <v>90</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5974,19 +5779,19 @@
         <v>90</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5995,7 +5800,7 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -6006,7 +5811,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -6021,19 +5826,19 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -6042,19 +5847,19 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -6063,10 +5868,10 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6074,7 +5879,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -6089,19 +5894,19 @@
         <v>50</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -6110,19 +5915,19 @@
         <v>50</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -6131,7 +5936,7 @@
         <v>50</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -6142,7 +5947,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -6157,19 +5962,19 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -6178,19 +5983,19 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -6199,7 +6004,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6210,7 +6015,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -6225,19 +6030,19 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -6246,19 +6051,19 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6267,7 +6072,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6278,7 +6083,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -6293,19 +6098,19 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -6314,19 +6119,19 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6335,7 +6140,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6346,7 +6151,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -6361,19 +6166,19 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -6382,19 +6187,19 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q32">
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -6403,7 +6208,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6414,7 +6219,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -6429,19 +6234,19 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -6450,19 +6255,19 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6471,7 +6276,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -6482,7 +6287,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -6497,19 +6302,19 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -6518,19 +6323,19 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O34">
         <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -6539,7 +6344,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6550,7 +6355,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6565,19 +6370,19 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>100</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -6586,19 +6391,19 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6607,10 +6412,10 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V35">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6618,7 +6423,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6633,19 +6438,19 @@
         <v>100</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6654,19 +6459,19 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6675,7 +6480,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6686,7 +6491,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6701,19 +6506,19 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>100</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -6722,19 +6527,19 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O37">
         <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="Q37">
         <v>100</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -6743,7 +6548,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V37">
         <v>100</v>
@@ -6754,7 +6559,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6769,19 +6574,19 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -6790,19 +6595,19 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="Q38">
         <v>100</v>
       </c>
       <c r="R38">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -6811,10 +6616,10 @@
         <v>100</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V38">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6822,7 +6627,7 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6837,19 +6642,19 @@
         <v>90</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>100</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6858,19 +6663,19 @@
         <v>90</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O39">
         <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q39">
         <v>100</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -6879,7 +6684,7 @@
         <v>90</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -6890,7 +6695,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -6905,13 +6710,13 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>100</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -6926,13 +6731,13 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="O40">
         <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6947,7 +6752,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -7007,7 +6812,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -7016,27 +6821,30 @@
         <v>37</v>
       </c>
       <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2">
+        <v>35.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="H2">
+        <v>5.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>37</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -7045,27 +6853,30 @@
         <v>37</v>
       </c>
       <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>23</v>
+      </c>
+      <c r="F3" s="2">
+        <v>37.8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>62.2</v>
+      </c>
+      <c r="H3">
+        <v>5.7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3" s="2">
         <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>37</v>
-      </c>
-      <c r="J3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -7074,19 +6885,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2">
-        <v>35.1</v>
+        <v>40.5</v>
       </c>
       <c r="G4" s="2">
-        <v>64.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7097,7 +6908,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -7106,19 +6917,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2">
-        <v>45.9</v>
+        <v>48.6</v>
       </c>
       <c r="G5" s="2">
-        <v>54.1</v>
+        <v>51.4</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7161,7 +6972,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -7182,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7202,19 +7013,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2">
-        <v>81.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="G8" s="2">
-        <v>18.9</v>
+        <v>24.3</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7250,7 +7061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7277,1486 +7088,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920282</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920282</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920322</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920322</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920281</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920281</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920283</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920283</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920284</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920284</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920347</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920347</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920339</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920339</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920285</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920285</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920293</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920293</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920292</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920292</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920317</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920317</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920350</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920350</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920294</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920294</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920356</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>144</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920356</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920295</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920295</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920352</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>146</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920352</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920296</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920296</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920298</v>
-      </c>
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>23330051920298</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>23330051920297</v>
-      </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D38" t="s">
-        <v>149</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>23330051920297</v>
-      </c>
-      <c r="B39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" t="s">
-        <v>149</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>23330051920336</v>
-      </c>
-      <c r="B40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>150</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>23330051920336</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>23330051920362</v>
-      </c>
-      <c r="B42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>151</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>23330051920362</v>
-      </c>
-      <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" t="s">
-        <v>151</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>23330051920299</v>
-      </c>
-      <c r="B44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>23330051920299</v>
-      </c>
-      <c r="B45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" t="s">
-        <v>112</v>
-      </c>
-      <c r="D45" t="s">
-        <v>152</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>23330051920340</v>
-      </c>
-      <c r="B46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>23330051920340</v>
-      </c>
-      <c r="B47" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>23330051920301</v>
-      </c>
-      <c r="B48" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" t="s">
-        <v>154</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>23330051920301</v>
-      </c>
-      <c r="B49" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" t="s">
-        <v>82</v>
-      </c>
-      <c r="D49" t="s">
-        <v>154</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>23330051920308</v>
-      </c>
-      <c r="B50" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" t="s">
-        <v>5</v>
-      </c>
-      <c r="F50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>23330051920308</v>
-      </c>
-      <c r="B51" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" t="s">
-        <v>155</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>23330051920310</v>
-      </c>
-      <c r="B52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" t="s">
-        <v>125</v>
-      </c>
-      <c r="D52" t="s">
-        <v>156</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>23330051920310</v>
-      </c>
-      <c r="B53" t="s">
-        <v>97</v>
-      </c>
-      <c r="C53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D53" t="s">
-        <v>156</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>23330051920309</v>
-      </c>
-      <c r="B54" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" t="s">
-        <v>157</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>23330051920309</v>
-      </c>
-      <c r="B55" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>23330051920314</v>
-      </c>
-      <c r="B56" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" t="s">
-        <v>158</v>
-      </c>
-      <c r="E56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>23330051920314</v>
-      </c>
-      <c r="B57" t="s">
-        <v>99</v>
-      </c>
-      <c r="C57" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>23330051920348</v>
-      </c>
-      <c r="B58" t="s">
-        <v>100</v>
-      </c>
-      <c r="C58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58" t="s">
-        <v>159</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>23330051920348</v>
-      </c>
-      <c r="B59" t="s">
-        <v>100</v>
-      </c>
-      <c r="C59" t="s">
-        <v>89</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>23330051920363</v>
-      </c>
-      <c r="B60" t="s">
-        <v>101</v>
-      </c>
-      <c r="C60" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>23330051920363</v>
-      </c>
-      <c r="B61" t="s">
-        <v>101</v>
-      </c>
-      <c r="C61" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61" t="s">
-        <v>160</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>23330051920326</v>
-      </c>
-      <c r="B62" t="s">
-        <v>102</v>
-      </c>
-      <c r="C62" t="s">
-        <v>127</v>
-      </c>
-      <c r="D62" t="s">
-        <v>161</v>
-      </c>
-      <c r="E62" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>23330051920326</v>
-      </c>
-      <c r="B63" t="s">
-        <v>102</v>
-      </c>
-      <c r="C63" t="s">
-        <v>127</v>
-      </c>
-      <c r="D63" t="s">
-        <v>161</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>23330051920311</v>
-      </c>
-      <c r="B64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
-      </c>
-      <c r="D64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>23330051920311</v>
-      </c>
-      <c r="B65" t="s">
-        <v>103</v>
-      </c>
-      <c r="C65" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" t="s">
-        <v>162</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>23330051920353</v>
-      </c>
-      <c r="B66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" t="s">
-        <v>129</v>
-      </c>
-      <c r="D66" t="s">
-        <v>163</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>23330051920353</v>
-      </c>
-      <c r="B67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>23330051920345</v>
-      </c>
-      <c r="B68" t="s">
-        <v>105</v>
-      </c>
-      <c r="C68" t="s">
-        <v>116</v>
-      </c>
-      <c r="D68" t="s">
-        <v>164</v>
-      </c>
-      <c r="E68" t="s">
-        <v>5</v>
-      </c>
-      <c r="F68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>23330051920345</v>
-      </c>
-      <c r="B69" t="s">
-        <v>105</v>
-      </c>
-      <c r="C69" t="s">
-        <v>116</v>
-      </c>
-      <c r="D69" t="s">
-        <v>164</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>23330051920312</v>
-      </c>
-      <c r="B70" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" t="s">
-        <v>116</v>
-      </c>
-      <c r="D70" t="s">
-        <v>165</v>
-      </c>
-      <c r="E70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>23330051920312</v>
-      </c>
-      <c r="B71" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" t="s">
-        <v>165</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>23330051920343</v>
-      </c>
-      <c r="B72" t="s">
-        <v>107</v>
-      </c>
-      <c r="C72" t="s">
-        <v>83</v>
-      </c>
-      <c r="D72" t="s">
-        <v>166</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>23330051920343</v>
-      </c>
-      <c r="B73" t="s">
-        <v>107</v>
-      </c>
-      <c r="C73" t="s">
-        <v>83</v>
-      </c>
-      <c r="D73" t="s">
-        <v>166</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>23330051920320</v>
-      </c>
-      <c r="B74" t="s">
-        <v>108</v>
-      </c>
-      <c r="C74" t="s">
-        <v>130</v>
-      </c>
-      <c r="D74" t="s">
-        <v>167</v>
-      </c>
-      <c r="E74" t="s">
-        <v>5</v>
-      </c>
-      <c r="F74" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>23330051920320</v>
-      </c>
-      <c r="B75" t="s">
-        <v>108</v>
-      </c>
-      <c r="C75" t="s">
-        <v>130</v>
-      </c>
-      <c r="D75" t="s">
-        <v>167</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8764,7 +7095,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8796,186 +7127,347 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920322</v>
+        <v>23330051920356</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920322</v>
+        <v>23330051920356</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920296</v>
+        <v>23330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920296</v>
+        <v>23330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920297</v>
+        <v>23330051920310</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920297</v>
+        <v>23330051920310</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920345</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
         <v>97</v>
       </c>
-      <c r="C9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920345</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920295</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920336</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920348</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920320</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -209,10 +209,13 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
+    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
@@ -221,9 +224,6 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -245,27 +245,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>GARZA</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DEL VALLE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -275,21 +269,18 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
     <t>MOLINA</t>
   </si>
   <si>
@@ -299,25 +290,19 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
     <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>ALDRICH ARMANDO</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
   </si>
   <si>
     <t>IVETTE</t>
@@ -862,10 +847,10 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>9</v>
@@ -951,10 +936,10 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>9</v>
@@ -993,10 +978,10 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -1040,10 +1025,10 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>6</v>
@@ -1085,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1129,10 +1114,10 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -1218,10 +1203,10 @@
         <v>4</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>8</v>
@@ -1263,7 +1248,7 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>7</v>
@@ -1307,10 +1292,10 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>8</v>
@@ -1349,10 +1334,10 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1396,10 +1381,10 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1441,7 +1426,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1485,10 +1470,10 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -1574,10 +1559,10 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>7</v>
@@ -1619,7 +1604,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1663,10 +1648,10 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>8</v>
@@ -1705,10 +1690,10 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1752,10 +1737,10 @@
         <v>4</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -1797,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB14">
         <v>8</v>
@@ -1841,10 +1826,10 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -1930,10 +1915,10 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>6</v>
@@ -1972,7 +1957,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2019,10 +2004,10 @@
         <v>4</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -2064,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2108,10 +2093,10 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>6</v>
@@ -2150,7 +2135,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2197,10 +2182,10 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>8</v>
@@ -2242,7 +2227,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>9</v>
@@ -2286,10 +2271,10 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -2331,7 +2316,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -2375,10 +2360,10 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>9</v>
@@ -2420,7 +2405,7 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2464,10 +2449,10 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>10</v>
@@ -2506,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2553,10 +2538,10 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>9</v>
@@ -2598,7 +2583,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2642,10 +2627,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -2687,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2731,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -2820,10 +2805,10 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>8</v>
@@ -2862,7 +2847,7 @@
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>5</v>
@@ -2909,10 +2894,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>5</v>
@@ -2998,10 +2983,10 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>6</v>
@@ -3087,10 +3072,10 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -3176,10 +3161,10 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>7</v>
@@ -3265,10 +3250,10 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>9</v>
@@ -3310,7 +3295,7 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3354,10 +3339,10 @@
         <v>4</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>8</v>
@@ -3443,10 +3428,10 @@
         <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>10</v>
@@ -3488,7 +3473,7 @@
         <v>7</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB33">
         <v>10</v>
@@ -3532,10 +3517,10 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>9</v>
@@ -3574,10 +3559,10 @@
         <v>5</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>8</v>
@@ -3621,10 +3606,10 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>5</v>
@@ -3710,10 +3695,10 @@
         <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>6</v>
@@ -3755,7 +3740,7 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>7</v>
@@ -3799,10 +3784,10 @@
         <v>4</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>6</v>
@@ -3844,7 +3829,7 @@
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB37">
         <v>6</v>
@@ -3888,10 +3873,10 @@
         <v>4</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>5</v>
@@ -3977,10 +3962,10 @@
         <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -4066,10 +4051,10 @@
         <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>5</v>
@@ -4481,7 +4466,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4502,7 +4487,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -4685,7 +4670,7 @@
         <v>93.2</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4706,7 +4691,7 @@
         <v>93.2</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4756,7 +4741,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N11">
         <v>96.8</v>
@@ -4777,7 +4762,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="U11">
         <v>96.8</v>
@@ -4889,7 +4874,7 @@
         <v>97.7</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4910,7 +4895,7 @@
         <v>97.7</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5025,10 +5010,10 @@
         <v>93.2</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N15">
         <v>96.8</v>
@@ -5046,10 +5031,10 @@
         <v>93.2</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U15">
         <v>96.8</v>
@@ -5300,7 +5285,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N19">
         <v>96.8</v>
@@ -5321,7 +5306,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U19">
         <v>96.8</v>
@@ -5365,7 +5350,7 @@
         <v>97.7</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -5386,7 +5371,7 @@
         <v>97.7</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5433,7 +5418,7 @@
         <v>97.7</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5454,7 +5439,7 @@
         <v>97.7</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5569,7 +5554,7 @@
         <v>97.7</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -5590,7 +5575,7 @@
         <v>97.7</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5637,10 +5622,10 @@
         <v>43.2</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="M24">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="N24">
         <v>96.8</v>
@@ -5658,10 +5643,10 @@
         <v>43.2</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="T24">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U24">
         <v>96.8</v>
@@ -5705,10 +5690,10 @@
         <v>81.8</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M25">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="N25">
         <v>96.8</v>
@@ -5726,10 +5711,10 @@
         <v>81.8</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T25">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U25">
         <v>96.8</v>
@@ -5773,10 +5758,10 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M26">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N26">
         <v>96.8</v>
@@ -5794,10 +5779,10 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T26">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="U26">
         <v>96.8</v>
@@ -5841,10 +5826,10 @@
         <v>54.5</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N27">
         <v>96.8</v>
@@ -5862,10 +5847,10 @@
         <v>54.5</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="U27">
         <v>96.8</v>
@@ -5912,7 +5897,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>50</v>
+        <v>72.5</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -5933,7 +5918,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>50</v>
+        <v>72.5</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5977,7 +5962,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5998,7 +5983,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6385,7 +6370,7 @@
         <v>77.3</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -6406,7 +6391,7 @@
         <v>77.3</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -6453,7 +6438,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -6474,7 +6459,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6521,7 +6506,7 @@
         <v>77.3</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6542,7 +6527,7 @@
         <v>77.3</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6589,7 +6574,7 @@
         <v>77.3</v>
       </c>
       <c r="L38">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M38">
         <v>100</v>
@@ -6610,7 +6595,7 @@
         <v>77.3</v>
       </c>
       <c r="S38">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T38">
         <v>100</v>
@@ -6657,10 +6642,10 @@
         <v>77.3</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M39">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N39">
         <v>96.8</v>
@@ -6678,10 +6663,10 @@
         <v>77.3</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T39">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U39">
         <v>96.8</v>
@@ -6812,7 +6797,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6821,19 +6806,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2">
-        <v>35.1</v>
+        <v>37.8</v>
       </c>
       <c r="G2" s="2">
-        <v>64.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6844,7 +6829,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6853,19 +6838,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
       <c r="G3" s="2">
-        <v>62.2</v>
+        <v>59.5</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6876,7 +6861,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6897,7 +6882,7 @@
         <v>59.5</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6908,7 +6893,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -6917,19 +6902,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
-        <v>48.6</v>
+        <v>40.5</v>
       </c>
       <c r="G5" s="2">
-        <v>51.4</v>
+        <v>59.5</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6940,7 +6925,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -6949,19 +6934,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2">
-        <v>54.1</v>
+        <v>48.6</v>
       </c>
       <c r="G6" s="2">
-        <v>45.9</v>
+        <v>51.4</v>
       </c>
       <c r="H6">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7095,7 +7080,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7127,19 +7112,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920356</v>
+        <v>23330051920299</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
@@ -7150,19 +7135,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920356</v>
+        <v>23330051920299</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -7173,22 +7158,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920299</v>
+        <v>23330051920310</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7196,19 +7181,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920299</v>
+        <v>23330051920310</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -7219,22 +7204,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7242,22 +7227,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7265,22 +7250,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920363</v>
+        <v>23330051920311</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7288,22 +7273,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920363</v>
+        <v>23330051920311</v>
       </c>
       <c r="B9" t="s">
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7311,19 +7296,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920345</v>
+        <v>23330051920356</v>
       </c>
       <c r="B10" t="s">
         <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -7334,22 +7319,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920345</v>
+        <v>23330051920336</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7357,19 +7342,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920292</v>
+        <v>23330051920348</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>67</v>
@@ -7380,93 +7365,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920295</v>
+        <v>23330051920320</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
         <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920336</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920348</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920320</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="104">
   <si>
     <t>Materia</t>
   </si>
@@ -224,12 +224,12 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -245,28 +245,52 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
     <t>PERALTA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>GARZA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -275,19 +299,25 @@
     <t>HERRERA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>APALE</t>
+    <t>MARIANA JANET</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JURISEL</t>
+  </si>
+  <si>
+    <t>JENNYFER ARIANA</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
   </si>
   <si>
     <t>MICHEL LEONEL</t>
@@ -296,22 +326,10 @@
     <t>JESHUA</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>AARON</t>
-  </si>
-  <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -862,22 +880,22 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -886,7 +904,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -895,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -951,31 +969,31 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>6</v>
@@ -984,10 +1002,10 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1040,22 +1058,22 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1070,13 +1088,13 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>6</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1129,22 +1147,22 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1153,7 +1171,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1218,22 +1236,22 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1242,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1254,7 +1272,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1307,22 +1325,22 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1331,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>6</v>
@@ -1396,22 +1414,22 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1420,7 +1438,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1429,7 +1447,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1485,28 +1503,28 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1574,22 +1592,22 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1604,13 +1622,13 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1663,22 +1681,22 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1752,28 +1770,28 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1785,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -1841,28 +1859,28 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1930,22 +1948,22 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -2019,22 +2037,22 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2108,22 +2126,22 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2132,7 +2150,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -2197,22 +2215,22 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2227,13 +2245,13 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2286,22 +2304,22 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2310,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2375,22 +2393,22 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2399,7 +2417,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>7</v>
@@ -2408,7 +2426,7 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2464,22 +2482,22 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2488,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2500,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2553,22 +2571,22 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2583,7 +2601,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2642,22 +2660,22 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2731,22 +2749,22 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2820,22 +2838,22 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2844,19 +2862,19 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2909,22 +2927,22 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2998,22 +3016,22 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3087,22 +3105,22 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -3117,13 +3135,13 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3176,22 +3194,22 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3209,7 +3227,7 @@
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3265,22 +3283,22 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3289,16 +3307,16 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -3354,22 +3372,22 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3390,7 +3408,7 @@
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3443,28 +3461,28 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3473,13 +3491,13 @@
         <v>7</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3532,22 +3550,22 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3556,7 +3574,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3621,22 +3639,22 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>5</v>
@@ -3710,22 +3728,22 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3734,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3799,22 +3817,22 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S37">
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3888,28 +3906,28 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>5</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -3977,28 +3995,28 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>7</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -4010,7 +4028,7 @@
         <v>5</v>
       </c>
       <c r="AB39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC39">
         <v>5</v>
@@ -4066,28 +4084,28 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>8</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -4096,7 +4114,7 @@
         <v>6</v>
       </c>
       <c r="AA40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB40">
         <v>7</v>
@@ -4280,7 +4298,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4289,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4348,7 +4366,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4357,7 +4375,7 @@
         <v>95</v>
       </c>
       <c r="U5">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4416,7 +4434,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4425,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4484,19 +4502,19 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>84.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S7">
         <v>93.8</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U7">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V7">
-        <v>94</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4552,16 +4570,16 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U8">
-        <v>80.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4620,16 +4638,16 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U9">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -4688,19 +4706,19 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>93.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S10">
         <v>87.5</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U10">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V10">
-        <v>90</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4756,16 +4774,16 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U11">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4824,7 +4842,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4833,7 +4851,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>80.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4892,7 +4910,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="S13">
         <v>93.8</v>
@@ -4901,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4960,7 +4978,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>88.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4969,7 +4987,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -5028,16 +5046,16 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S15">
         <v>84.40000000000001</v>
       </c>
       <c r="T15">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U15">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -5096,16 +5114,16 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U16">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5164,16 +5182,16 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U17">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5232,16 +5250,16 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U18">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5300,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5309,7 +5327,7 @@
         <v>95</v>
       </c>
       <c r="U19">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5368,16 +5386,16 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>97.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S20">
         <v>93.8</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U20">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5436,7 +5454,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="S21">
         <v>93.8</v>
@@ -5445,7 +5463,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5504,7 +5522,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5513,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5572,7 +5590,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S23">
         <v>96.90000000000001</v>
@@ -5581,7 +5599,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5637,22 +5655,22 @@
         <v>77.8</v>
       </c>
       <c r="Q24">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="R24">
-        <v>43.2</v>
+        <v>29.7</v>
       </c>
       <c r="S24">
         <v>68.8</v>
       </c>
       <c r="T24">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U24">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V24">
-        <v>88</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5708,16 +5726,16 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="S25">
         <v>75</v>
       </c>
       <c r="T25">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U25">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5776,16 +5794,16 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S26">
         <v>84.40000000000001</v>
       </c>
       <c r="T26">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="U26">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5841,22 +5859,22 @@
         <v>66.7</v>
       </c>
       <c r="Q27">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="R27">
-        <v>54.5</v>
+        <v>37.5</v>
       </c>
       <c r="S27">
         <v>50</v>
       </c>
       <c r="T27">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U27">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V27">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5912,13 +5930,13 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5980,7 +5998,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>90.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S29">
         <v>81.3</v>
@@ -5989,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6048,16 +6066,16 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U30">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6116,7 +6134,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6125,7 +6143,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6184,7 +6202,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>97.7</v>
+        <v>93.8</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -6193,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6252,7 +6270,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6261,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -6320,7 +6338,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -6329,7 +6347,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6388,7 +6406,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>77.3</v>
+        <v>62.5</v>
       </c>
       <c r="S35">
         <v>50</v>
@@ -6397,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V35">
-        <v>88</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6456,16 +6474,16 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S36">
         <v>96.90000000000001</v>
       </c>
       <c r="T36">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U36">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6524,16 +6542,16 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>77.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S37">
         <v>93.8</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U37">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V37">
         <v>100</v>
@@ -6589,22 +6607,22 @@
         <v>77.8</v>
       </c>
       <c r="Q38">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R38">
-        <v>77.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S38">
         <v>75</v>
       </c>
       <c r="T38">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U38">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V38">
-        <v>90</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6660,7 +6678,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>77.3</v>
+        <v>79.7</v>
       </c>
       <c r="S39">
         <v>90.59999999999999</v>
@@ -6669,7 +6687,7 @@
         <v>95</v>
       </c>
       <c r="U39">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -6737,7 +6755,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -6870,19 +6888,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2">
-        <v>40.5</v>
+        <v>48.6</v>
       </c>
       <c r="G4" s="2">
-        <v>59.5</v>
+        <v>51.4</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6902,19 +6920,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2">
-        <v>40.5</v>
+        <v>51.4</v>
       </c>
       <c r="G5" s="2">
-        <v>59.5</v>
+        <v>48.6</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6934,19 +6952,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2">
-        <v>48.6</v>
+        <v>54.1</v>
       </c>
       <c r="G6" s="2">
-        <v>51.4</v>
+        <v>45.9</v>
       </c>
       <c r="H6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6957,7 +6975,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6978,7 +6996,7 @@
         <v>27</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6989,7 +7007,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -6998,19 +7016,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2">
-        <v>75.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>24.3</v>
+        <v>21.6</v>
       </c>
       <c r="H8">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7080,7 +7098,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7112,16 +7130,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920299</v>
+        <v>23330051920282</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7135,22 +7153,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920299</v>
+        <v>23330051920282</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7158,16 +7176,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920310</v>
+        <v>23330051920284</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7181,22 +7199,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920310</v>
+        <v>23330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7204,16 +7222,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920363</v>
+        <v>23330051920285</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7227,22 +7245,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920363</v>
+        <v>23330051920285</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7250,16 +7268,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920311</v>
+        <v>23330051920281</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7273,22 +7291,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920311</v>
+        <v>23330051920356</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7296,22 +7314,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920356</v>
+        <v>23330051920336</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7319,22 +7337,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920336</v>
+        <v>23330051920299</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7342,22 +7360,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920348</v>
+        <v>23330051920310</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7365,24 +7383,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920320</v>
+        <v>23330051920348</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920363</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -248,15 +248,21 @@
     <t>AVILA</t>
   </si>
   <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>BERTELY</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
     <t>GARZA</t>
   </si>
   <si>
@@ -278,15 +284,21 @@
     <t>PABLO</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GALINDO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -305,13 +317,19 @@
     <t>MARIANA JANET</t>
   </si>
   <si>
+    <t>LUCIA</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
     <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
   </si>
   <si>
     <t>JENNYFER ARIANA</t>
@@ -877,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -966,7 +984,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -987,7 +1005,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1055,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1144,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1233,7 +1251,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1254,7 +1272,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1322,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1343,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1411,7 +1429,7 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1432,7 +1450,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1500,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1589,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>6</v>
@@ -1678,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1767,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -1856,7 +1874,7 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1945,7 +1963,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -2034,7 +2052,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -2123,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -2144,7 +2162,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2212,7 +2230,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2301,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -2390,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2411,7 +2429,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2479,7 +2497,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2500,7 +2518,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2568,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>8</v>
@@ -2657,7 +2675,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2746,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>5</v>
@@ -2835,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -2924,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -3013,7 +3031,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>5</v>
@@ -3102,7 +3120,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3123,7 +3141,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3191,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -3280,7 +3298,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -3369,7 +3387,7 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -3458,7 +3476,7 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -3547,7 +3565,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>8</v>
@@ -3636,7 +3654,7 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>7</v>
@@ -3725,7 +3743,7 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>8</v>
@@ -3746,7 +3764,7 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3814,7 +3832,7 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>5</v>
@@ -3903,7 +3921,7 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -3992,7 +4010,7 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -4013,7 +4031,7 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39">
         <v>5</v>
@@ -4081,7 +4099,7 @@
         <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>4</v>
@@ -4360,7 +4378,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4428,7 +4446,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>94.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4496,7 +4514,7 @@
         <v>94</v>
       </c>
       <c r="P7">
-        <v>72.2</v>
+        <v>80</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4564,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>94.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4700,7 +4718,7 @@
         <v>90</v>
       </c>
       <c r="P10">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4768,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4836,7 +4854,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4904,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>88.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4972,7 +4990,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>94.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5040,7 +5058,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5108,7 +5126,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -5176,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5244,7 +5262,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5312,7 +5330,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5448,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5516,7 +5534,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>94.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5584,7 +5602,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5652,7 +5670,7 @@
         <v>88</v>
       </c>
       <c r="P24">
-        <v>77.8</v>
+        <v>80</v>
       </c>
       <c r="Q24">
         <v>77.8</v>
@@ -5720,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5788,7 +5806,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>72.2</v>
+        <v>80</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5856,7 +5874,7 @@
         <v>80</v>
       </c>
       <c r="P27">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="Q27">
         <v>73.3</v>
@@ -5924,7 +5942,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>72.2</v>
+        <v>80</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5992,7 +6010,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>72.2</v>
+        <v>83.3</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -6060,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -6128,7 +6146,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -6196,7 +6214,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6264,7 +6282,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>94.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6332,7 +6350,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>72.2</v>
+        <v>80</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6400,7 +6418,7 @@
         <v>88</v>
       </c>
       <c r="P35">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6468,7 +6486,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6536,7 +6554,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6604,7 +6622,7 @@
         <v>90</v>
       </c>
       <c r="P38">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="Q38">
         <v>88.90000000000001</v>
@@ -6672,7 +6690,7 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -6740,7 +6758,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>88.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6815,7 +6833,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6824,19 +6842,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
       <c r="G2" s="2">
-        <v>62.2</v>
+        <v>59.5</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6847,7 +6865,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6856,19 +6874,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2">
-        <v>40.5</v>
+        <v>48.6</v>
       </c>
       <c r="G3" s="2">
-        <v>59.5</v>
+        <v>51.4</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6879,7 +6897,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6888,19 +6906,19 @@
         <v>37</v>
       </c>
       <c r="D4">
+        <v>19</v>
+      </c>
+      <c r="E4">
         <v>18</v>
       </c>
-      <c r="E4">
-        <v>19</v>
-      </c>
       <c r="F4" s="2">
+        <v>51.4</v>
+      </c>
+      <c r="G4" s="2">
         <v>48.6</v>
       </c>
-      <c r="G4" s="2">
-        <v>51.4</v>
-      </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7098,7 +7116,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7136,16 +7154,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7159,16 +7177,16 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7176,22 +7194,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920284</v>
+        <v>23330051920347</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7199,22 +7217,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920284</v>
+        <v>23330051920347</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7228,16 +7246,16 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7251,16 +7269,16 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7268,22 +7286,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920281</v>
+        <v>23330051920308</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7291,22 +7309,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920356</v>
+        <v>23330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7314,22 +7332,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920336</v>
+        <v>23330051920311</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7337,19 +7355,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920299</v>
+        <v>23330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>63</v>
@@ -7360,19 +7378,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920310</v>
+        <v>23330051920284</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>63</v>
@@ -7383,22 +7401,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920348</v>
+        <v>23330051920356</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7406,24 +7424,116 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920363</v>
+        <v>23330051920336</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>63</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920299</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920310</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920348</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920363</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -209,27 +209,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -245,109 +245,94 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
     <t>AVILA</t>
   </si>
   <si>
-    <t>CASANOVA</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>GARZA</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>LUCIA</t>
   </si>
   <si>
     <t>MARIANA JANET</t>
   </si>
   <si>
-    <t>LUCIA</t>
-  </si>
-  <si>
     <t>DANIEL DE JESUS</t>
   </si>
   <si>
+    <t>JENNYFER ARIANA</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
     <t>JUSTIN GIOVANNI</t>
   </si>
   <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
     <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>AARON</t>
   </si>
 </sst>
 </file>
@@ -904,7 +889,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -925,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>9</v>
@@ -993,7 +978,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -1014,7 +999,7 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1082,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1103,7 +1088,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1171,7 +1156,7 @@
         <v>4</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1192,7 +1177,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1260,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1281,7 +1266,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -1349,7 +1334,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1438,7 +1423,7 @@
         <v>4</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1459,7 +1444,7 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1527,7 +1512,7 @@
         <v>4</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1616,7 +1601,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1637,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1705,7 +1690,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1794,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1815,7 +1800,7 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -1883,7 +1868,7 @@
         <v>4</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1904,7 +1889,7 @@
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>5</v>
@@ -1972,7 +1957,7 @@
         <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1993,7 +1978,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2061,7 +2046,7 @@
         <v>4</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -2150,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2171,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2239,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2260,7 +2245,7 @@
         <v>7</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2328,7 +2313,7 @@
         <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2417,7 +2402,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2438,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2506,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2595,7 +2580,7 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2616,7 +2601,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2684,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2773,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2862,7 +2847,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2951,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -3040,7 +3025,7 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -3061,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -3129,7 +3114,7 @@
         <v>4</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -3150,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3218,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>5</v>
@@ -3239,7 +3224,7 @@
         <v>6</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>5</v>
@@ -3307,7 +3292,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3328,7 +3313,7 @@
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3396,7 +3381,7 @@
         <v>4</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -3485,7 +3470,7 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3506,7 +3491,7 @@
         <v>6</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3574,7 +3559,7 @@
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3595,7 +3580,7 @@
         <v>7</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -3663,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>5</v>
@@ -3752,7 +3737,7 @@
         <v>4</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3773,7 +3758,7 @@
         <v>5</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>6</v>
@@ -3841,7 +3826,7 @@
         <v>4</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3862,7 +3847,7 @@
         <v>5</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>5</v>
@@ -3930,7 +3915,7 @@
         <v>4</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>5</v>
@@ -3951,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
         <v>5</v>
@@ -4019,7 +4004,7 @@
         <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -4040,7 +4025,7 @@
         <v>5</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
         <v>5</v>
@@ -4108,7 +4093,7 @@
         <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -4129,7 +4114,7 @@
         <v>7</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA40">
         <v>5</v>
@@ -4523,7 +4508,7 @@
         <v>82.8</v>
       </c>
       <c r="S7">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="T7">
         <v>95</v>
@@ -4727,7 +4712,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S10">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T10">
         <v>98.3</v>
@@ -4795,7 +4780,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T11">
         <v>96.7</v>
@@ -4931,7 +4916,7 @@
         <v>95.3</v>
       </c>
       <c r="S13">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5067,7 +5052,7 @@
         <v>92.2</v>
       </c>
       <c r="S15">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T15">
         <v>96.7</v>
@@ -5407,7 +5392,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S20">
-        <v>93.8</v>
+        <v>70.8</v>
       </c>
       <c r="T20">
         <v>98.3</v>
@@ -5475,7 +5460,7 @@
         <v>95.3</v>
       </c>
       <c r="S21">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5611,7 +5596,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S23">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5679,7 +5664,7 @@
         <v>29.7</v>
       </c>
       <c r="S24">
-        <v>68.8</v>
+        <v>45.8</v>
       </c>
       <c r="T24">
         <v>90</v>
@@ -5747,7 +5732,7 @@
         <v>75</v>
       </c>
       <c r="S25">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T25">
         <v>90</v>
@@ -5815,7 +5800,7 @@
         <v>87.5</v>
       </c>
       <c r="S26">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T26">
         <v>93.3</v>
@@ -5883,7 +5868,7 @@
         <v>37.5</v>
       </c>
       <c r="S27">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T27">
         <v>50</v>
@@ -6019,7 +6004,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S29">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6087,7 +6072,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T30">
         <v>98.3</v>
@@ -6291,7 +6276,7 @@
         <v>95.3</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T33">
         <v>100</v>
@@ -6427,7 +6412,7 @@
         <v>62.5</v>
       </c>
       <c r="S35">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -6495,7 +6480,7 @@
         <v>87.5</v>
       </c>
       <c r="S36">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T36">
         <v>98.3</v>
@@ -6563,7 +6548,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="S37">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T37">
         <v>98.3</v>
@@ -6631,7 +6616,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="S38">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="T38">
         <v>98.3</v>
@@ -6699,7 +6684,7 @@
         <v>79.7</v>
       </c>
       <c r="S39">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T39">
         <v>95</v>
@@ -6833,7 +6818,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6842,19 +6827,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2">
-        <v>40.5</v>
+        <v>48.6</v>
       </c>
       <c r="G2" s="2">
-        <v>59.5</v>
+        <v>51.4</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6865,7 +6850,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6874,19 +6859,19 @@
         <v>37</v>
       </c>
       <c r="D3">
+        <v>19</v>
+      </c>
+      <c r="E3">
         <v>18</v>
       </c>
-      <c r="E3">
-        <v>19</v>
-      </c>
       <c r="F3" s="2">
+        <v>51.4</v>
+      </c>
+      <c r="G3" s="2">
         <v>48.6</v>
       </c>
-      <c r="G3" s="2">
-        <v>51.4</v>
-      </c>
       <c r="H3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6897,7 +6882,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6918,7 +6903,7 @@
         <v>48.6</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6929,7 +6914,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -6938,19 +6923,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2">
-        <v>51.4</v>
+        <v>54.1</v>
       </c>
       <c r="G5" s="2">
-        <v>48.6</v>
+        <v>45.9</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6961,7 +6946,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -6970,19 +6955,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>54.1</v>
+        <v>73</v>
       </c>
       <c r="G6" s="2">
-        <v>45.9</v>
+        <v>27</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6993,7 +6978,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -7002,19 +6987,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2">
-        <v>73</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>27</v>
+        <v>21.6</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7025,7 +7010,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -7034,19 +7019,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>78.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="G8" s="2">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7116,7 +7101,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7148,22 +7133,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920282</v>
+        <v>23330051920347</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7171,22 +7156,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920282</v>
+        <v>23330051920347</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7194,19 +7179,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920347</v>
+        <v>23330051920282</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
@@ -7217,22 +7202,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920347</v>
+        <v>23330051920285</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7240,19 +7225,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920285</v>
+        <v>23330051920356</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -7263,22 +7248,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920285</v>
+        <v>23330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7289,19 +7274,19 @@
         <v>23330051920308</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
         <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7309,22 +7294,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920308</v>
+        <v>23330051920310</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
         <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7332,13 +7317,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920311</v>
+        <v>23330051920348</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
         <v>102</v>
@@ -7347,7 +7332,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7355,22 +7340,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920311</v>
+        <v>23330051920363</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7378,162 +7363,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920284</v>
+        <v>23330051920311</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920356</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920336</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920299</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920310</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920348</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920363</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -206,9 +209,6 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Recursos socioemocionales I</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -224,13 +224,13 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>NC</t>
@@ -694,13 +694,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AG40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -711,35 +711,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,77 +769,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -859,72 +875,84 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>7</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>9</v>
       </c>
       <c r="O4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q4">
+        <v>10</v>
+      </c>
+      <c r="R4">
+        <v>10</v>
+      </c>
+      <c r="S4">
         <v>9</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>9</v>
       </c>
-      <c r="S4">
-        <v>10</v>
-      </c>
-      <c r="T4">
-        <v>8</v>
-      </c>
       <c r="U4">
+        <v>10</v>
+      </c>
+      <c r="V4">
+        <v>8</v>
+      </c>
+      <c r="W4">
         <v>9</v>
       </c>
-      <c r="V4">
-        <v>8</v>
-      </c>
-      <c r="W4">
-        <v>8</v>
-      </c>
       <c r="X4">
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>8</v>
       </c>
       <c r="AA4">
+        <v>8</v>
+      </c>
+      <c r="AB4">
+        <v>8</v>
+      </c>
+      <c r="AC4">
+        <v>8</v>
+      </c>
+      <c r="AD4">
         <v>9</v>
       </c>
-      <c r="AB4">
+      <c r="AE4">
         <v>9</v>
       </c>
-      <c r="AC4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AF4">
+        <v>8</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -948,72 +976,84 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
         <v>9</v>
       </c>
-      <c r="O5">
-        <v>5</v>
-      </c>
       <c r="P5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>7</v>
+      </c>
+      <c r="U5">
         <v>9</v>
       </c>
-      <c r="T5">
-        <v>7</v>
-      </c>
-      <c r="U5">
-        <v>7</v>
-      </c>
       <c r="V5">
         <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD5">
+        <v>7</v>
+      </c>
+      <c r="AE5">
+        <v>8</v>
+      </c>
+      <c r="AF5">
+        <v>6</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1040,34 +1080,34 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1079,30 +1119,42 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6">
+        <v>6</v>
+      </c>
+      <c r="AE6">
+        <v>6</v>
+      </c>
+      <c r="AF6">
+        <v>6</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1126,20 +1178,20 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
         <v>4</v>
       </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
       <c r="N7">
         <v>5</v>
       </c>
@@ -1150,48 +1202,60 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7">
+        <v>7</v>
+      </c>
+      <c r="T7">
         <v>4</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>9</v>
       </c>
-      <c r="T7">
-        <v>5</v>
-      </c>
-      <c r="U7">
-        <v>8</v>
-      </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD7">
+        <v>5</v>
+      </c>
+      <c r="AE7">
+        <v>7</v>
+      </c>
+      <c r="AF7">
+        <v>5</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -1215,72 +1279,84 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8">
+        <v>7</v>
+      </c>
+      <c r="L8">
         <v>4</v>
       </c>
-      <c r="L8">
-        <v>5</v>
-      </c>
       <c r="M8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>8</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>7</v>
       </c>
       <c r="S8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>7</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>7</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>6</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1304,31 +1380,31 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>7</v>
@@ -1337,39 +1413,51 @@
         <v>7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>6</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB9">
+        <v>6</v>
+      </c>
+      <c r="AC9">
+        <v>6</v>
+      </c>
+      <c r="AD9">
+        <v>5</v>
+      </c>
+      <c r="AE9">
         <v>9</v>
       </c>
-      <c r="AC9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AF9">
+        <v>5</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -1393,19 +1481,19 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1414,51 +1502,63 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q10">
+        <v>10</v>
+      </c>
+      <c r="R10">
+        <v>7</v>
+      </c>
+      <c r="S10">
         <v>9</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>4</v>
       </c>
-      <c r="S10">
-        <v>8</v>
-      </c>
-      <c r="T10">
-        <v>5</v>
-      </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD10">
+        <v>5</v>
+      </c>
+      <c r="AE10">
+        <v>6</v>
+      </c>
+      <c r="AF10">
+        <v>5</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -1482,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1491,13 +1591,13 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1506,22 +1606,22 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R11">
+        <v>6</v>
+      </c>
+      <c r="S11">
+        <v>7</v>
+      </c>
+      <c r="T11">
         <v>4</v>
       </c>
-      <c r="S11">
-        <v>7</v>
-      </c>
-      <c r="T11">
-        <v>5</v>
-      </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1530,24 +1630,36 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>6</v>
+      </c>
+      <c r="AF11">
+        <v>5</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -1571,72 +1683,84 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>5</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>6</v>
       </c>
       <c r="S12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12">
+        <v>6</v>
+      </c>
+      <c r="AE12">
+        <v>7</v>
+      </c>
+      <c r="AF12">
+        <v>6</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1660,72 +1784,84 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
         <v>9</v>
       </c>
-      <c r="K13">
-        <v>6</v>
-      </c>
       <c r="L13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13">
+        <v>8</v>
+      </c>
+      <c r="N13">
         <v>9</v>
       </c>
-      <c r="N13">
-        <v>8</v>
-      </c>
       <c r="O13">
+        <v>8</v>
+      </c>
+      <c r="P13">
         <v>9</v>
       </c>
-      <c r="P13">
-        <v>7</v>
-      </c>
       <c r="Q13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>7</v>
       </c>
       <c r="S13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>9</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
+        <v>6</v>
+      </c>
+      <c r="AC13">
+        <v>8</v>
+      </c>
+      <c r="AD13">
+        <v>7</v>
+      </c>
+      <c r="AE13">
         <v>9</v>
       </c>
-      <c r="AC13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AF13">
+        <v>8</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1749,22 +1885,22 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>6</v>
       </c>
       <c r="K14">
+        <v>6</v>
+      </c>
+      <c r="L14">
         <v>4</v>
       </c>
-      <c r="L14">
-        <v>6</v>
-      </c>
       <c r="M14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1776,25 +1912,25 @@
         <v>5</v>
       </c>
       <c r="R14">
+        <v>6</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
+      </c>
+      <c r="T14">
         <v>4</v>
       </c>
-      <c r="S14">
-        <v>7</v>
-      </c>
-      <c r="T14">
-        <v>5</v>
-      </c>
       <c r="U14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1806,15 +1942,27 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>5</v>
+      </c>
+      <c r="AE14">
+        <v>7</v>
+      </c>
+      <c r="AF14">
+        <v>6</v>
+      </c>
+      <c r="AG14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1838,7 +1986,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1856,28 +2004,28 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R15">
+        <v>6</v>
+      </c>
+      <c r="S15">
+        <v>7</v>
+      </c>
+      <c r="T15">
         <v>4</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>9</v>
       </c>
-      <c r="T15">
-        <v>5</v>
-      </c>
-      <c r="U15">
-        <v>5</v>
-      </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1886,24 +2034,36 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>5</v>
+      </c>
+      <c r="AF15">
+        <v>5</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1927,19 +2087,19 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>6</v>
@@ -1951,13 +2111,13 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1966,33 +2126,45 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:29">
+      <c r="AD16">
+        <v>5</v>
+      </c>
+      <c r="AE16">
+        <v>7</v>
+      </c>
+      <c r="AF16">
+        <v>6</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2019,17 +2191,17 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17">
+        <v>6</v>
+      </c>
+      <c r="L17">
         <v>4</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>3</v>
       </c>
-      <c r="M17">
-        <v>5</v>
-      </c>
       <c r="N17">
         <v>5</v>
       </c>
@@ -2037,20 +2209,20 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R17">
+        <v>6</v>
+      </c>
+      <c r="S17">
+        <v>5</v>
+      </c>
+      <c r="T17">
         <v>4</v>
       </c>
-      <c r="S17">
-        <v>5</v>
-      </c>
-      <c r="T17">
-        <v>5</v>
-      </c>
       <c r="U17">
         <v>5</v>
       </c>
@@ -2078,10 +2250,22 @@
       <c r="AC17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AD17">
+        <v>5</v>
+      </c>
+      <c r="AE17">
+        <v>5</v>
+      </c>
+      <c r="AF17">
+        <v>5</v>
+      </c>
+      <c r="AG17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -2105,72 +2289,84 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>6</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18">
+        <v>5</v>
+      </c>
+      <c r="Q18">
+        <v>10</v>
+      </c>
+      <c r="R18">
         <v>9</v>
       </c>
-      <c r="Q18">
-        <v>6</v>
-      </c>
-      <c r="R18">
-        <v>8</v>
-      </c>
       <c r="S18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
+        <v>8</v>
+      </c>
+      <c r="V18">
+        <v>7</v>
+      </c>
+      <c r="W18">
         <v>9</v>
       </c>
-      <c r="V18">
-        <v>7</v>
-      </c>
-      <c r="W18">
-        <v>8</v>
-      </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD18">
+        <v>6</v>
+      </c>
+      <c r="AE18">
+        <v>8</v>
+      </c>
+      <c r="AF18">
+        <v>5</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -2194,72 +2390,84 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M19">
+        <v>8</v>
+      </c>
+      <c r="N19">
         <v>9</v>
       </c>
-      <c r="N19">
-        <v>8</v>
-      </c>
       <c r="O19">
+        <v>8</v>
+      </c>
+      <c r="P19">
         <v>9</v>
       </c>
-      <c r="P19">
-        <v>7</v>
-      </c>
       <c r="Q19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>7</v>
       </c>
       <c r="S19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19">
+        <v>7</v>
+      </c>
+      <c r="U19">
+        <v>10</v>
+      </c>
+      <c r="V19">
         <v>9</v>
       </c>
-      <c r="U19">
-        <v>6</v>
-      </c>
-      <c r="V19">
-        <v>7</v>
-      </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z19">
+        <v>6</v>
+      </c>
+      <c r="AA19">
+        <v>8</v>
+      </c>
+      <c r="AB19">
+        <v>7</v>
+      </c>
+      <c r="AC19">
         <v>9</v>
       </c>
-      <c r="AA19">
-        <v>8</v>
-      </c>
-      <c r="AB19">
-        <v>8</v>
-      </c>
-      <c r="AC19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19">
+        <v>8</v>
+      </c>
+      <c r="AE19">
+        <v>8</v>
+      </c>
+      <c r="AF19">
+        <v>7</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -2289,14 +2497,14 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
         <v>3</v>
       </c>
-      <c r="M20">
-        <v>5</v>
-      </c>
       <c r="N20">
         <v>5</v>
       </c>
@@ -2322,16 +2530,16 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2340,15 +2548,27 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:29">
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>5</v>
+      </c>
+      <c r="AF20">
+        <v>5</v>
+      </c>
+      <c r="AG20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -2372,72 +2592,84 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N21">
+        <v>8</v>
+      </c>
+      <c r="O21">
         <v>9</v>
       </c>
-      <c r="O21">
-        <v>10</v>
-      </c>
       <c r="P21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S21">
+        <v>8</v>
+      </c>
+      <c r="T21">
+        <v>5</v>
+      </c>
+      <c r="U21">
         <v>9</v>
       </c>
-      <c r="T21">
-        <v>6</v>
-      </c>
-      <c r="U21">
-        <v>6</v>
-      </c>
       <c r="V21">
+        <v>6</v>
+      </c>
+      <c r="W21">
+        <v>6</v>
+      </c>
+      <c r="X21">
         <v>9</v>
       </c>
-      <c r="W21">
-        <v>7</v>
-      </c>
-      <c r="X21">
-        <v>7</v>
-      </c>
       <c r="Y21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC21">
+        <v>8</v>
+      </c>
+      <c r="AD21">
+        <v>7</v>
+      </c>
+      <c r="AE21">
+        <v>8</v>
+      </c>
+      <c r="AF21">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>6</v>
@@ -2461,20 +2693,20 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22">
         <v>9</v>
       </c>
-      <c r="K22">
-        <v>7</v>
-      </c>
       <c r="L22">
+        <v>7</v>
+      </c>
+      <c r="M22">
         <v>9</v>
       </c>
-      <c r="M22">
-        <v>10</v>
-      </c>
       <c r="N22">
         <v>10</v>
       </c>
@@ -2500,33 +2732,45 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC22">
+        <v>8</v>
+      </c>
+      <c r="AD22">
+        <v>10</v>
+      </c>
+      <c r="AE22">
+        <v>10</v>
+      </c>
+      <c r="AF22">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:29">
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -2550,31 +2794,31 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>8</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N23">
+        <v>8</v>
+      </c>
+      <c r="O23">
         <v>9</v>
       </c>
-      <c r="O23">
-        <v>10</v>
-      </c>
       <c r="P23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2583,39 +2827,51 @@
         <v>8</v>
       </c>
       <c r="T23">
+        <v>8</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+      <c r="V23">
         <v>9</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>9</v>
       </c>
-      <c r="V23">
-        <v>7</v>
-      </c>
-      <c r="W23">
-        <v>8</v>
-      </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD23">
+        <v>8</v>
+      </c>
+      <c r="AE23">
+        <v>8</v>
+      </c>
+      <c r="AF23">
+        <v>8</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2645,14 +2901,14 @@
         <v>5</v>
       </c>
       <c r="K24">
+        <v>5</v>
+      </c>
+      <c r="L24">
         <v>0</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>3</v>
       </c>
-      <c r="M24">
-        <v>5</v>
-      </c>
       <c r="N24">
         <v>5</v>
       </c>
@@ -2666,14 +2922,14 @@
         <v>5</v>
       </c>
       <c r="R24">
+        <v>5</v>
+      </c>
+      <c r="S24">
+        <v>5</v>
+      </c>
+      <c r="T24">
         <v>0</v>
       </c>
-      <c r="S24">
-        <v>5</v>
-      </c>
-      <c r="T24">
-        <v>5</v>
-      </c>
       <c r="U24">
         <v>5</v>
       </c>
@@ -2701,10 +2957,22 @@
       <c r="AC24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:29">
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>5</v>
+      </c>
+      <c r="AF24">
+        <v>5</v>
+      </c>
+      <c r="AG24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -2734,14 +3002,14 @@
         <v>5</v>
       </c>
       <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
         <v>4</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>3</v>
       </c>
-      <c r="M25">
-        <v>5</v>
-      </c>
       <c r="N25">
         <v>5</v>
       </c>
@@ -2755,14 +3023,14 @@
         <v>5</v>
       </c>
       <c r="R25">
+        <v>5</v>
+      </c>
+      <c r="S25">
+        <v>5</v>
+      </c>
+      <c r="T25">
         <v>0</v>
       </c>
-      <c r="S25">
-        <v>5</v>
-      </c>
-      <c r="T25">
-        <v>5</v>
-      </c>
       <c r="U25">
         <v>5</v>
       </c>
@@ -2790,10 +3058,22 @@
       <c r="AC25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:29">
+      <c r="AD25">
+        <v>5</v>
+      </c>
+      <c r="AE25">
+        <v>5</v>
+      </c>
+      <c r="AF25">
+        <v>5</v>
+      </c>
+      <c r="AG25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -2817,72 +3097,84 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>6</v>
       </c>
       <c r="S26">
+        <v>8</v>
+      </c>
+      <c r="T26">
+        <v>6</v>
+      </c>
+      <c r="U26">
         <v>9</v>
       </c>
-      <c r="T26">
-        <v>7</v>
-      </c>
-      <c r="U26">
-        <v>8</v>
-      </c>
       <c r="V26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD26">
+        <v>6</v>
+      </c>
+      <c r="AE26">
+        <v>8</v>
+      </c>
+      <c r="AF26">
+        <v>6</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>5</v>
@@ -2912,11 +3204,11 @@
         <v>5</v>
       </c>
       <c r="K27">
+        <v>5</v>
+      </c>
+      <c r="L27">
         <v>0</v>
       </c>
-      <c r="L27">
-        <v>5</v>
-      </c>
       <c r="M27">
         <v>5</v>
       </c>
@@ -2927,20 +3219,20 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>5</v>
       </c>
       <c r="R27">
+        <v>6</v>
+      </c>
+      <c r="S27">
+        <v>5</v>
+      </c>
+      <c r="T27">
         <v>0</v>
       </c>
-      <c r="S27">
-        <v>5</v>
-      </c>
-      <c r="T27">
-        <v>5</v>
-      </c>
       <c r="U27">
         <v>5</v>
       </c>
@@ -2968,10 +3260,22 @@
       <c r="AC27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:29">
+      <c r="AD27">
+        <v>5</v>
+      </c>
+      <c r="AE27">
+        <v>5</v>
+      </c>
+      <c r="AF27">
+        <v>5</v>
+      </c>
+      <c r="AG27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -2995,72 +3299,84 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>5</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>6</v>
       </c>
       <c r="S28">
+        <v>5</v>
+      </c>
+      <c r="T28">
+        <v>6</v>
+      </c>
+      <c r="U28">
         <v>9</v>
       </c>
-      <c r="T28">
-        <v>5</v>
-      </c>
-      <c r="U28">
-        <v>8</v>
-      </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD28">
+        <v>5</v>
+      </c>
+      <c r="AE28">
+        <v>8</v>
+      </c>
+      <c r="AF28">
+        <v>5</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3084,13 +3400,13 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -3105,51 +3421,63 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R29">
+        <v>7</v>
+      </c>
+      <c r="S29">
+        <v>7</v>
+      </c>
+      <c r="T29">
         <v>4</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>9</v>
       </c>
-      <c r="T29">
-        <v>8</v>
-      </c>
-      <c r="U29">
-        <v>7</v>
-      </c>
       <c r="V29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z29">
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:29">
+      <c r="AD29">
+        <v>6</v>
+      </c>
+      <c r="AE29">
+        <v>6</v>
+      </c>
+      <c r="AF29">
+        <v>6</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -3173,72 +3501,84 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>9</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD30">
+        <v>5</v>
+      </c>
+      <c r="AE30">
+        <v>7</v>
+      </c>
+      <c r="AF30">
+        <v>5</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -3262,72 +3602,84 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>9</v>
       </c>
       <c r="O31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U31">
+        <v>10</v>
+      </c>
+      <c r="V31">
+        <v>6</v>
+      </c>
+      <c r="W31">
         <v>9</v>
       </c>
-      <c r="V31">
+      <c r="X31">
         <v>9</v>
       </c>
-      <c r="W31">
-        <v>5</v>
-      </c>
-      <c r="X31">
-        <v>8</v>
-      </c>
       <c r="Y31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
+        <v>6</v>
+      </c>
+      <c r="AC31">
+        <v>8</v>
+      </c>
+      <c r="AD31">
+        <v>7</v>
+      </c>
+      <c r="AE31">
         <v>9</v>
       </c>
-      <c r="AC31">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
+      <c r="AF31">
+        <v>8</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>6</v>
@@ -3351,41 +3703,41 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K32">
+        <v>7</v>
+      </c>
+      <c r="L32">
         <v>4</v>
       </c>
-      <c r="L32">
-        <v>7</v>
-      </c>
       <c r="M32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O32">
+        <v>8</v>
+      </c>
+      <c r="P32">
         <v>9</v>
       </c>
-      <c r="P32">
-        <v>6</v>
-      </c>
       <c r="Q32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R32">
+        <v>6</v>
+      </c>
+      <c r="S32">
+        <v>7</v>
+      </c>
+      <c r="T32">
         <v>4</v>
       </c>
-      <c r="S32">
-        <v>8</v>
-      </c>
-      <c r="T32">
-        <v>6</v>
-      </c>
       <c r="U32">
         <v>8</v>
       </c>
@@ -3393,30 +3745,42 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>6</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC32">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD32">
+        <v>6</v>
+      </c>
+      <c r="AE32">
+        <v>7</v>
+      </c>
+      <c r="AF32">
+        <v>8</v>
+      </c>
+      <c r="AG32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>9</v>
@@ -3440,7 +3804,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -3452,28 +3816,28 @@
         <v>7</v>
       </c>
       <c r="M33">
+        <v>7</v>
+      </c>
+      <c r="N33">
         <v>9</v>
       </c>
-      <c r="N33">
-        <v>10</v>
-      </c>
       <c r="O33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3482,30 +3846,42 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z33">
         <v>8</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC33">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:29">
+      <c r="AD33">
+        <v>8</v>
+      </c>
+      <c r="AE33">
+        <v>10</v>
+      </c>
+      <c r="AF33">
+        <v>8</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3529,72 +3905,84 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>8</v>
       </c>
       <c r="N34">
+        <v>8</v>
+      </c>
+      <c r="O34">
         <v>9</v>
       </c>
-      <c r="O34">
-        <v>8</v>
-      </c>
       <c r="P34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R34">
+        <v>7</v>
+      </c>
+      <c r="S34">
+        <v>8</v>
+      </c>
+      <c r="T34">
         <v>9</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>9</v>
       </c>
-      <c r="T34">
-        <v>8</v>
-      </c>
-      <c r="U34">
-        <v>8</v>
-      </c>
       <c r="V34">
         <v>8</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA34">
         <v>7</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD34">
+        <v>7</v>
+      </c>
+      <c r="AE34">
+        <v>8</v>
+      </c>
+      <c r="AF34">
+        <v>7</v>
+      </c>
+      <c r="AG34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -3621,13 +4009,13 @@
         <v>5</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3639,20 +4027,20 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R35">
+        <v>6</v>
+      </c>
+      <c r="S35">
+        <v>7</v>
+      </c>
+      <c r="T35">
         <v>0</v>
       </c>
-      <c r="S35">
-        <v>5</v>
-      </c>
-      <c r="T35">
-        <v>5</v>
-      </c>
       <c r="U35">
         <v>5</v>
       </c>
@@ -3663,7 +4051,7 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3672,7 +4060,7 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>5</v>
@@ -3680,10 +4068,22 @@
       <c r="AC35">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:29">
+      <c r="AD35">
+        <v>5</v>
+      </c>
+      <c r="AE35">
+        <v>5</v>
+      </c>
+      <c r="AF35">
+        <v>5</v>
+      </c>
+      <c r="AG35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -3707,72 +4107,84 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L36">
+        <v>6</v>
+      </c>
+      <c r="M36">
         <v>3</v>
       </c>
-      <c r="M36">
-        <v>7</v>
-      </c>
       <c r="N36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O36">
+        <v>6</v>
+      </c>
+      <c r="P36">
         <v>9</v>
       </c>
-      <c r="P36">
-        <v>7</v>
-      </c>
       <c r="Q36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R36">
+        <v>7</v>
+      </c>
+      <c r="S36">
+        <v>8</v>
+      </c>
+      <c r="T36">
         <v>4</v>
       </c>
-      <c r="S36">
-        <v>10</v>
-      </c>
-      <c r="T36">
-        <v>6</v>
-      </c>
       <c r="U36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V36">
+        <v>6</v>
+      </c>
+      <c r="W36">
+        <v>8</v>
+      </c>
+      <c r="X36">
         <v>9</v>
       </c>
-      <c r="W36">
-        <v>6</v>
-      </c>
-      <c r="X36">
-        <v>7</v>
-      </c>
       <c r="Y36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z36">
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC36">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD36">
+        <v>6</v>
+      </c>
+      <c r="AE36">
+        <v>7</v>
+      </c>
+      <c r="AF36">
+        <v>8</v>
+      </c>
+      <c r="AG36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>7</v>
@@ -3802,37 +4214,37 @@
         <v>5</v>
       </c>
       <c r="K37">
+        <v>5</v>
+      </c>
+      <c r="L37">
         <v>4</v>
       </c>
-      <c r="L37">
-        <v>5</v>
-      </c>
       <c r="M37">
         <v>5</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>5</v>
       </c>
       <c r="R37">
+        <v>6</v>
+      </c>
+      <c r="S37">
+        <v>5</v>
+      </c>
+      <c r="T37">
         <v>4</v>
       </c>
-      <c r="S37">
-        <v>8</v>
-      </c>
-      <c r="T37">
-        <v>5</v>
-      </c>
       <c r="U37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>5</v>
@@ -3853,15 +4265,27 @@
         <v>5</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD37">
+        <v>5</v>
+      </c>
+      <c r="AE37">
+        <v>6</v>
+      </c>
+      <c r="AF37">
+        <v>5</v>
+      </c>
+      <c r="AG37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -3885,19 +4309,19 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>5</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>4</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N38">
         <v>5</v>
@@ -3906,23 +4330,23 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>5</v>
       </c>
       <c r="R38">
+        <v>6</v>
+      </c>
+      <c r="S38">
+        <v>5</v>
+      </c>
+      <c r="T38">
         <v>4</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>9</v>
       </c>
-      <c r="T38">
-        <v>5</v>
-      </c>
-      <c r="U38">
-        <v>5</v>
-      </c>
       <c r="V38">
         <v>5</v>
       </c>
@@ -3930,27 +4354,39 @@
         <v>5</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y38">
         <v>5</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD38">
+        <v>5</v>
+      </c>
+      <c r="AE38">
+        <v>5</v>
+      </c>
+      <c r="AF38">
+        <v>5</v>
+      </c>
+      <c r="AG38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>9</v>
@@ -3974,7 +4410,7 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J39">
         <v>5</v>
@@ -3983,11 +4419,11 @@
         <v>5</v>
       </c>
       <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="M39">
         <v>3</v>
       </c>
-      <c r="M39">
-        <v>5</v>
-      </c>
       <c r="N39">
         <v>5</v>
       </c>
@@ -3995,22 +4431,22 @@
         <v>5</v>
       </c>
       <c r="P39">
+        <v>5</v>
+      </c>
+      <c r="Q39">
+        <v>5</v>
+      </c>
+      <c r="R39">
         <v>3</v>
       </c>
-      <c r="Q39">
+      <c r="S39">
         <v>4</v>
       </c>
-      <c r="R39">
-        <v>5</v>
-      </c>
-      <c r="S39">
-        <v>10</v>
-      </c>
       <c r="T39">
         <v>5</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -4025,21 +4461,33 @@
         <v>5</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA39">
         <v>5</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD39">
+        <v>5</v>
+      </c>
+      <c r="AE39">
+        <v>6</v>
+      </c>
+      <c r="AF39">
+        <v>5</v>
+      </c>
+      <c r="AG39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>8</v>
@@ -4063,13 +4511,13 @@
         <v>5</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>6</v>
@@ -4078,43 +4526,43 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>5</v>
       </c>
       <c r="P40">
+        <v>5</v>
+      </c>
+      <c r="Q40">
+        <v>10</v>
+      </c>
+      <c r="R40">
         <v>9</v>
       </c>
-      <c r="Q40">
+      <c r="S40">
         <v>4</v>
       </c>
-      <c r="R40">
-        <v>7</v>
-      </c>
-      <c r="S40">
-        <v>8</v>
-      </c>
       <c r="T40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>5</v>
@@ -4123,15 +4571,27 @@
         <v>7</v>
       </c>
       <c r="AC40">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="AD40">
+        <v>5</v>
+      </c>
+      <c r="AE40">
+        <v>7</v>
+      </c>
+      <c r="AF40">
+        <v>5</v>
+      </c>
+      <c r="AG40">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4139,16 +4599,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4156,26 +4616,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4201,56 +4664,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4274,7 +4746,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4289,36 +4761,45 @@
         <v>100</v>
       </c>
       <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
         <v>96.8</v>
       </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>96.90000000000001</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
       <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
         <v>97.8</v>
       </c>
-      <c r="V4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -4342,51 +4823,60 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>97.7</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
       <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>95</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>96.8</v>
       </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R5">
         <v>96.7</v>
       </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>96.90000000000001</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5">
         <v>95</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>97.8</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4410,51 +4900,60 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>94.40000000000001</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>97.7</v>
       </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
         <v>96.8</v>
       </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
       <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R6">
         <v>90</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>96.90000000000001</v>
       </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>100</v>
-      </c>
       <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+      <c r="W6">
         <v>97.8</v>
       </c>
-      <c r="V6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="X6">
+        <v>100</v>
+      </c>
+      <c r="Y6">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -4478,51 +4977,60 @@
         <v>100</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>72.2</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>84.09999999999999</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>93.8</v>
       </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
       <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
         <v>96.8</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>94</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R7">
         <v>80</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>82.8</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>91.7</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>95</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>97.8</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Y7">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>90</v>
@@ -4546,51 +5054,60 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>94.40000000000001</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>93.2</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>80.59999999999999</v>
       </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>90</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>93.8</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>96.7</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>87</v>
       </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -4614,51 +5131,60 @@
         <v>100</v>
       </c>
       <c r="I9">
+        <v>93.8</v>
+      </c>
+      <c r="J9">
         <v>83.3</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
       <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>90.90000000000001</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>96.8</v>
       </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R9">
         <v>83.3</v>
       </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
         <v>92.2</v>
       </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
         <v>98.3</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>97.8</v>
       </c>
-      <c r="V9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="X9">
+        <v>100</v>
+      </c>
+      <c r="Y9">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>80</v>
@@ -4682,51 +5208,60 @@
         <v>100</v>
       </c>
       <c r="I10">
+        <v>93.8</v>
+      </c>
+      <c r="J10">
         <v>83.3</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>93.2</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>87.5</v>
       </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
       <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
         <v>96.8</v>
-      </c>
-      <c r="O10">
-        <v>90</v>
       </c>
       <c r="P10">
         <v>90</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R10">
+        <v>90</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>89.09999999999999</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>91.7</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>98.3</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>97.8</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Y10">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -4750,51 +5285,60 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>93.8</v>
+      </c>
+      <c r="J11">
         <v>94.40000000000001</v>
       </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>93.2</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
         <v>97.5</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>96.8</v>
       </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R11">
         <v>96.7</v>
       </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>90.59999999999999</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>95.8</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>96.7</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>97.8</v>
       </c>
-      <c r="V11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="X11">
+        <v>100</v>
+      </c>
+      <c r="Y11">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -4818,51 +5362,60 @@
         <v>100</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>88.90000000000001</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>93.2</v>
       </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
         <v>80.59999999999999</v>
       </c>
-      <c r="O12">
-        <v>100</v>
-      </c>
       <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>90</v>
       </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>92.2</v>
       </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
       <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>87</v>
       </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="X12">
+        <v>100</v>
+      </c>
+      <c r="Y12">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -4886,51 +5439,60 @@
         <v>100</v>
       </c>
       <c r="I13">
+        <v>93.8</v>
+      </c>
+      <c r="J13">
         <v>88.90000000000001</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>97.7</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>93.8</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>96.8</v>
       </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>93.8</v>
+      </c>
+      <c r="R13">
         <v>93.3</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>95.3</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>95.8</v>
       </c>
-      <c r="T13">
-        <v>100</v>
-      </c>
-      <c r="U13">
+      <c r="V13">
+        <v>100</v>
+      </c>
+      <c r="W13">
         <v>97.8</v>
       </c>
-      <c r="V13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="X13">
+        <v>100</v>
+      </c>
+      <c r="Y13">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4954,51 +5516,60 @@
         <v>100</v>
       </c>
       <c r="I14">
+        <v>93.8</v>
+      </c>
+      <c r="J14">
         <v>94.40000000000001</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>88.59999999999999</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>96.8</v>
       </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>93.8</v>
+      </c>
+      <c r="R14">
         <v>93.3</v>
       </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>81.3</v>
       </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-      <c r="T14">
-        <v>100</v>
-      </c>
       <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
         <v>97.8</v>
       </c>
-      <c r="V14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="X14">
+        <v>100</v>
+      </c>
+      <c r="Y14">
+        <v>89.59999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>90</v>
@@ -5022,51 +5593,60 @@
         <v>100</v>
       </c>
       <c r="I15">
+        <v>93.8</v>
+      </c>
+      <c r="J15">
         <v>83.3</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>93.2</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>84.40000000000001</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>95</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>96.8</v>
       </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
       <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R15">
         <v>86.7</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>92.2</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>89.59999999999999</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>96.7</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>97.8</v>
       </c>
-      <c r="V15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="X15">
+        <v>100</v>
+      </c>
+      <c r="Y15">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -5090,51 +5670,60 @@
         <v>100</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>94.40000000000001</v>
       </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>93.2</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>96.8</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>96.7</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>90.59999999999999</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
         <v>98.3</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>97.8</v>
       </c>
-      <c r="V16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="X16">
+        <v>100</v>
+      </c>
+      <c r="Y16">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -5158,51 +5747,60 @@
         <v>100</v>
       </c>
       <c r="I17">
+        <v>93.8</v>
+      </c>
+      <c r="J17">
         <v>83.3</v>
       </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>90.90000000000001</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
         <v>96.8</v>
       </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
       <c r="P17">
+        <v>100</v>
+      </c>
+      <c r="Q17">
+        <v>81.3</v>
+      </c>
+      <c r="R17">
         <v>86.7</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>84.40000000000001</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
         <v>98.3</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>97.8</v>
       </c>
-      <c r="V17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="X17">
+        <v>100</v>
+      </c>
+      <c r="Y17">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -5226,51 +5824,60 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>93.8</v>
+      </c>
+      <c r="J18">
         <v>94.40000000000001</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>93.2</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
         <v>96.8</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>93.8</v>
+      </c>
+      <c r="R18">
         <v>96.7</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>93.8</v>
       </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
         <v>98.3</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>97.8</v>
       </c>
-      <c r="V18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="X18">
+        <v>100</v>
+      </c>
+      <c r="Y18">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -5294,51 +5901,60 @@
         <v>100</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>94.40000000000001</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>97.7</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
         <v>95</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>96.8</v>
       </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
       <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>96.7</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>92.2</v>
       </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
         <v>95</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>97.8</v>
       </c>
-      <c r="V19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="X19">
+        <v>100</v>
+      </c>
+      <c r="Y19">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>60</v>
@@ -5362,51 +5978,60 @@
         <v>100</v>
       </c>
       <c r="I20">
+        <v>87.5</v>
+      </c>
+      <c r="J20">
         <v>66.7</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>97.7</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>93.8</v>
       </c>
-      <c r="M20">
-        <v>100</v>
-      </c>
       <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
         <v>96.8</v>
       </c>
-      <c r="O20">
-        <v>100</v>
-      </c>
       <c r="P20">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <v>87.5</v>
+      </c>
+      <c r="R20">
         <v>66.7</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
         <v>90.59999999999999</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>70.8</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>98.3</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>97.8</v>
       </c>
-      <c r="V20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="X20">
+        <v>100</v>
+      </c>
+      <c r="Y20">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -5430,51 +6055,60 @@
         <v>100</v>
       </c>
       <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
         <v>94.40000000000001</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>97.7</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>93.8</v>
       </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
       <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
         <v>96.8</v>
       </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
       <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>96.7</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>95.3</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>95.8</v>
       </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
-      <c r="U21">
+      <c r="V21">
+        <v>100</v>
+      </c>
+      <c r="W21">
         <v>97.8</v>
       </c>
-      <c r="V21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="X21">
+        <v>100</v>
+      </c>
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -5498,51 +6132,60 @@
         <v>100</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>94.40000000000001</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>93.2</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
         <v>96.8</v>
       </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
       <c r="P22">
+        <v>100</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>93.3</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>92.2</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
-        <v>100</v>
-      </c>
       <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
+        <v>100</v>
+      </c>
+      <c r="W22">
         <v>97.8</v>
       </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="X22">
+        <v>100</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -5566,51 +6209,60 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>97.7</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>96.90000000000001</v>
       </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
         <v>96.8</v>
       </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>93.8</v>
+      </c>
+      <c r="R23">
         <v>96.7</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>98.40000000000001</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>97.90000000000001</v>
       </c>
-      <c r="T23">
-        <v>100</v>
-      </c>
-      <c r="U23">
+      <c r="V23">
+        <v>100</v>
+      </c>
+      <c r="W23">
         <v>97.8</v>
       </c>
-      <c r="V23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="X23">
+        <v>100</v>
+      </c>
+      <c r="Y23">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -5634,51 +6286,60 @@
         <v>100</v>
       </c>
       <c r="I24">
+        <v>62.5</v>
+      </c>
+      <c r="J24">
         <v>77.8</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>83.3</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>43.2</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>68.8</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>87.5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>96.8</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>88</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
+        <v>56.3</v>
+      </c>
+      <c r="R24">
         <v>80</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>77.8</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>29.7</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>45.8</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>90</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>97.8</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>90.59999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>60</v>
@@ -5702,51 +6363,60 @@
         <v>100</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>66.7</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
       <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
         <v>81.8</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>75</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>87.5</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>96.8</v>
       </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
       <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>87.5</v>
+      </c>
+      <c r="R25">
         <v>73.3</v>
       </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
         <v>75</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>50</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>90</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>97.8</v>
       </c>
-      <c r="V25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>70</v>
@@ -5770,51 +6440,60 @@
         <v>100</v>
       </c>
       <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
         <v>72.2</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
       <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>86.40000000000001</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>84.40000000000001</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>92.5</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>96.8</v>
       </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
       <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>80</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>87.5</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>89.59999999999999</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>93.3</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>97.8</v>
       </c>
-      <c r="V26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="X26">
+        <v>100</v>
+      </c>
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>60</v>
@@ -5838,51 +6517,60 @@
         <v>100</v>
       </c>
       <c r="I27">
+        <v>68.8</v>
+      </c>
+      <c r="J27">
         <v>66.7</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>80</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>54.5</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>50</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>75</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>96.8</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>80</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
+        <v>34.4</v>
+      </c>
+      <c r="R27">
         <v>73.3</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>73.3</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>37.5</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>33.3</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>50</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>97.8</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>84.40000000000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="Y27">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>70</v>
@@ -5906,51 +6594,60 @@
         <v>100</v>
       </c>
       <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
         <v>72.2</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>93.2</v>
       </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
       <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
         <v>72.5</v>
       </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R28">
         <v>80</v>
       </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>92.2</v>
       </c>
-      <c r="S28">
-        <v>100</v>
-      </c>
-      <c r="T28">
+      <c r="U28">
+        <v>100</v>
+      </c>
+      <c r="V28">
         <v>80</v>
       </c>
-      <c r="U28">
-        <v>100</v>
-      </c>
-      <c r="V28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="W28">
+        <v>100</v>
+      </c>
+      <c r="X28">
+        <v>100</v>
+      </c>
+      <c r="Y28">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>60</v>
@@ -5974,51 +6671,60 @@
         <v>100</v>
       </c>
       <c r="I29">
+        <v>87.5</v>
+      </c>
+      <c r="J29">
         <v>72.2</v>
       </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>90.90000000000001</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>81.3</v>
       </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
       <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
         <v>96.8</v>
       </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="R29">
         <v>83.3</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>85.90000000000001</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>83.3</v>
       </c>
-      <c r="T29">
-        <v>100</v>
-      </c>
-      <c r="U29">
+      <c r="V29">
+        <v>100</v>
+      </c>
+      <c r="W29">
         <v>97.8</v>
       </c>
-      <c r="V29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>70</v>
@@ -6042,51 +6748,60 @@
         <v>100</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>77.8</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>97.7</v>
       </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
+        <v>100</v>
+      </c>
+      <c r="O30">
         <v>96.8</v>
       </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
       <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R30">
         <v>86.7</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>96.90000000000001</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>95.8</v>
       </c>
-      <c r="T30">
+      <c r="V30">
         <v>98.3</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>97.8</v>
       </c>
-      <c r="V30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -6110,51 +6825,60 @@
         <v>100</v>
       </c>
       <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
         <v>88.90000000000001</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>90.90000000000001</v>
       </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
       <c r="M31">
         <v>100</v>
       </c>
       <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>96.8</v>
       </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
       <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>90</v>
       </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>87.5</v>
       </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>100</v>
-      </c>
       <c r="U31">
+        <v>100</v>
+      </c>
+      <c r="V31">
+        <v>100</v>
+      </c>
+      <c r="W31">
         <v>97.8</v>
       </c>
-      <c r="V31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="X31">
+        <v>100</v>
+      </c>
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -6178,51 +6902,60 @@
         <v>100</v>
       </c>
       <c r="I32">
+        <v>87.5</v>
+      </c>
+      <c r="J32">
         <v>83.3</v>
       </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
       <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
         <v>97.7</v>
       </c>
-      <c r="L32">
-        <v>100</v>
-      </c>
       <c r="M32">
         <v>100</v>
       </c>
       <c r="N32">
+        <v>100</v>
+      </c>
+      <c r="O32">
         <v>96.8</v>
       </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
       <c r="P32">
+        <v>100</v>
+      </c>
+      <c r="Q32">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R32">
         <v>86.7</v>
       </c>
-      <c r="Q32">
-        <v>100</v>
-      </c>
-      <c r="R32">
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
         <v>93.8</v>
       </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-      <c r="T32">
-        <v>100</v>
-      </c>
       <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
+        <v>100</v>
+      </c>
+      <c r="W32">
         <v>97.8</v>
       </c>
-      <c r="V32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="X32">
+        <v>100</v>
+      </c>
+      <c r="Y32">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -6246,51 +6979,60 @@
         <v>100</v>
       </c>
       <c r="I33">
+        <v>93.8</v>
+      </c>
+      <c r="J33">
         <v>94.40000000000001</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
       <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
         <v>93.2</v>
       </c>
-      <c r="L33">
-        <v>100</v>
-      </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="O33">
         <v>96.8</v>
       </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
       <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R33">
         <v>93.3</v>
       </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>95.3</v>
       </c>
-      <c r="S33">
+      <c r="U33">
         <v>95.8</v>
       </c>
-      <c r="T33">
-        <v>100</v>
-      </c>
-      <c r="U33">
+      <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
         <v>97.8</v>
       </c>
-      <c r="V33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="X33">
+        <v>100</v>
+      </c>
+      <c r="Y33">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>60</v>
@@ -6314,51 +7056,60 @@
         <v>100</v>
       </c>
       <c r="I34">
+        <v>87.5</v>
+      </c>
+      <c r="J34">
         <v>72.2</v>
       </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
       <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
         <v>90.90000000000001</v>
       </c>
-      <c r="L34">
-        <v>100</v>
-      </c>
       <c r="M34">
         <v>100</v>
       </c>
       <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
         <v>96.8</v>
       </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
       <c r="P34">
+        <v>100</v>
+      </c>
+      <c r="Q34">
+        <v>93.8</v>
+      </c>
+      <c r="R34">
         <v>80</v>
       </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
         <v>90.59999999999999</v>
       </c>
-      <c r="S34">
-        <v>100</v>
-      </c>
-      <c r="T34">
-        <v>100</v>
-      </c>
       <c r="U34">
+        <v>100</v>
+      </c>
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
         <v>97.8</v>
       </c>
-      <c r="V34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="X34">
+        <v>100</v>
+      </c>
+      <c r="Y34">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>80</v>
@@ -6382,51 +7133,60 @@
         <v>100</v>
       </c>
       <c r="I35">
+        <v>75</v>
+      </c>
+      <c r="J35">
         <v>77.8</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
       <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
         <v>77.3</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>50</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>0</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>96.8</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>88</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
+        <v>62.5</v>
+      </c>
+      <c r="R35">
         <v>83.3</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
         <v>62.5</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>33.3</v>
       </c>
-      <c r="T35">
+      <c r="V35">
         <v>0</v>
       </c>
-      <c r="U35">
+      <c r="W35">
         <v>97.8</v>
       </c>
-      <c r="V35">
+      <c r="X35">
         <v>90.59999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="Y35">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>80</v>
@@ -6450,51 +7210,60 @@
         <v>100</v>
       </c>
       <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
         <v>77.8</v>
       </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
       <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
         <v>86.40000000000001</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>96.90000000000001</v>
       </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
       <c r="N36">
+        <v>100</v>
+      </c>
+      <c r="O36">
         <v>96.8</v>
       </c>
-      <c r="O36">
-        <v>100</v>
-      </c>
       <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>83.3</v>
       </c>
-      <c r="Q36">
-        <v>100</v>
-      </c>
-      <c r="R36">
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
         <v>87.5</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>95.8</v>
       </c>
-      <c r="T36">
+      <c r="V36">
         <v>98.3</v>
       </c>
-      <c r="U36">
+      <c r="W36">
         <v>97.8</v>
       </c>
-      <c r="V36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="X36">
+        <v>100</v>
+      </c>
+      <c r="Y36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>80</v>
@@ -6518,51 +7287,60 @@
         <v>100</v>
       </c>
       <c r="I37">
+        <v>75</v>
+      </c>
+      <c r="J37">
         <v>77.8</v>
       </c>
-      <c r="J37">
-        <v>100</v>
-      </c>
       <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
         <v>77.3</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>93.8</v>
       </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
       <c r="N37">
+        <v>100</v>
+      </c>
+      <c r="O37">
         <v>96.8</v>
       </c>
-      <c r="O37">
-        <v>100</v>
-      </c>
       <c r="P37">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="R37">
         <v>83.3</v>
       </c>
-      <c r="Q37">
-        <v>100</v>
-      </c>
-      <c r="R37">
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
         <v>73.40000000000001</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>89.59999999999999</v>
       </c>
-      <c r="T37">
+      <c r="V37">
         <v>98.3</v>
       </c>
-      <c r="U37">
+      <c r="W37">
         <v>97.8</v>
       </c>
-      <c r="V37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="X37">
+        <v>100</v>
+      </c>
+      <c r="Y37">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>80</v>
@@ -6586,51 +7364,60 @@
         <v>100</v>
       </c>
       <c r="I38">
+        <v>93.8</v>
+      </c>
+      <c r="J38">
         <v>77.8</v>
       </c>
-      <c r="J38">
-        <v>100</v>
-      </c>
       <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
         <v>77.3</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>75</v>
       </c>
-      <c r="M38">
-        <v>100</v>
-      </c>
       <c r="N38">
+        <v>100</v>
+      </c>
+      <c r="O38">
         <v>96.8</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>90</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
+        <v>81.3</v>
+      </c>
+      <c r="R38">
         <v>83.3</v>
       </c>
-      <c r="Q38">
+      <c r="S38">
         <v>88.90000000000001</v>
       </c>
-      <c r="R38">
+      <c r="T38">
         <v>73.40000000000001</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>83.3</v>
       </c>
-      <c r="T38">
+      <c r="V38">
         <v>98.3</v>
       </c>
-      <c r="U38">
+      <c r="W38">
         <v>97.8</v>
       </c>
-      <c r="V38">
+      <c r="X38">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="Y38">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>90</v>
@@ -6654,51 +7441,60 @@
         <v>100</v>
       </c>
       <c r="I39">
+        <v>75</v>
+      </c>
+      <c r="J39">
         <v>83.3</v>
       </c>
-      <c r="J39">
-        <v>100</v>
-      </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
         <v>77.3</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>90.59999999999999</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>95</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>96.8</v>
       </c>
-      <c r="O39">
-        <v>100</v>
-      </c>
       <c r="P39">
+        <v>100</v>
+      </c>
+      <c r="Q39">
+        <v>68.8</v>
+      </c>
+      <c r="R39">
         <v>90</v>
       </c>
-      <c r="Q39">
-        <v>100</v>
-      </c>
-      <c r="R39">
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>79.7</v>
       </c>
-      <c r="S39">
+      <c r="U39">
         <v>93.8</v>
       </c>
-      <c r="T39">
+      <c r="V39">
         <v>95</v>
       </c>
-      <c r="U39">
+      <c r="W39">
         <v>97.8</v>
       </c>
-      <c r="V39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="X39">
+        <v>100</v>
+      </c>
+      <c r="Y39">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>80</v>
@@ -6722,11 +7518,11 @@
         <v>100</v>
       </c>
       <c r="I40">
+        <v>93.8</v>
+      </c>
+      <c r="J40">
         <v>88.90000000000001</v>
       </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
       <c r="K40">
         <v>100</v>
       </c>
@@ -6737,20 +7533,20 @@
         <v>100</v>
       </c>
       <c r="N40">
+        <v>100</v>
+      </c>
+      <c r="O40">
         <v>96.8</v>
       </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
       <c r="P40">
+        <v>100</v>
+      </c>
+      <c r="Q40">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R40">
         <v>93.3</v>
       </c>
-      <c r="Q40">
-        <v>100</v>
-      </c>
-      <c r="R40">
-        <v>100</v>
-      </c>
       <c r="S40">
         <v>100</v>
       </c>
@@ -6758,17 +7554,26 @@
         <v>100</v>
       </c>
       <c r="U40">
+        <v>100</v>
+      </c>
+      <c r="V40">
+        <v>100</v>
+      </c>
+      <c r="W40">
         <v>97.8</v>
       </c>
-      <c r="V40">
-        <v>100</v>
+      <c r="X40">
+        <v>100</v>
+      </c>
+      <c r="Y40">
+        <v>97.90000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6789,31 +7594,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6978,7 +7783,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6987,19 +7792,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>78.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="G7" s="2">
-        <v>21.6</v>
+        <v>27</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7010,7 +7815,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -7019,19 +7824,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2">
-        <v>83.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
       <c r="H8">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7042,21 +7847,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>83.8</v>
+      </c>
+      <c r="G9" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="H9">
+        <v>6.5</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7091,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7125,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -926,25 +926,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1027,25 +1027,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1131,22 +1131,22 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1232,19 +1232,19 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD7">
         <v>5</v>
       </c>
       <c r="AE7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1330,25 +1330,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1431,22 +1431,22 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD9">
         <v>5</v>
       </c>
       <c r="AE9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF9">
         <v>5</v>
@@ -1532,22 +1532,22 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>5</v>
       </c>
       <c r="AE10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF10">
         <v>5</v>
@@ -1633,22 +1633,22 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1737,22 +1737,22 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1835,25 +1835,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1936,7 +1936,7 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -1945,16 +1945,16 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>5</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>5</v>
@@ -2040,13 +2040,13 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>5</v>
@@ -2141,22 +2141,22 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD16">
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2340,22 +2340,22 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2441,25 +2441,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2643,25 +2643,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2744,16 +2744,16 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>10</v>
@@ -2762,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="AF22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2845,25 +2845,25 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -3151,22 +3151,22 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3356,16 +3356,16 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD28">
         <v>5</v>
       </c>
       <c r="AE28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF28">
         <v>5</v>
@@ -3451,25 +3451,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3555,19 +3555,19 @@
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD30">
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF30">
         <v>5</v>
@@ -3656,22 +3656,22 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3754,25 +3754,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3855,25 +3855,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE33">
         <v>10</v>
       </c>
       <c r="AF33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3959,22 +3959,22 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4060,7 +4060,7 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB35">
         <v>5</v>
@@ -4158,25 +4158,25 @@
         <v>10</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4259,7 +4259,7 @@
         <v>5</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA37">
         <v>5</v>
@@ -4268,13 +4268,13 @@
         <v>5</v>
       </c>
       <c r="AC37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD37">
         <v>5</v>
       </c>
       <c r="AE37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF37">
         <v>5</v>
@@ -4363,13 +4363,13 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB38">
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD38">
         <v>5</v>
@@ -4470,13 +4470,13 @@
         <v>5</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD39">
         <v>5</v>
       </c>
       <c r="AE39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF39">
         <v>5</v>
@@ -4562,22 +4562,22 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA40">
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD40">
         <v>5</v>
       </c>
       <c r="AE40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -7644,7 +7644,7 @@
         <v>51.4</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7676,7 +7676,7 @@
         <v>48.6</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>48.6</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7740,7 +7740,7 @@
         <v>45.9</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7772,7 +7772,7 @@
         <v>27</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7836,7 +7836,7 @@
         <v>21.6</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>16.2</v>
       </c>
       <c r="H9">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/grupos/1DV - Estadisticos 20231.xlsx
+++ b/grupos/1DV - Estadisticos 20231.xlsx
@@ -926,25 +926,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1027,25 +1027,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1131,22 +1131,22 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1232,19 +1232,19 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD7">
         <v>5</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1330,25 +1330,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1431,22 +1431,22 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD9">
         <v>5</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <v>5</v>
@@ -1532,22 +1532,22 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD10">
         <v>5</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF10">
         <v>5</v>
@@ -1633,22 +1633,22 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD11">
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1737,22 +1737,22 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1835,25 +1835,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1936,7 +1936,7 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -1945,16 +1945,16 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD14">
         <v>5</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG14">
         <v>5</v>
@@ -2040,13 +2040,13 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD15">
         <v>5</v>
@@ -2141,22 +2141,22 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD16">
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2340,22 +2340,22 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2441,25 +2441,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2643,25 +2643,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2744,16 +2744,16 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>10</v>
@@ -2762,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2845,25 +2845,25 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -3151,22 +3151,22 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3356,16 +3356,16 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD28">
         <v>5</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF28">
         <v>5</v>
@@ -3451,25 +3451,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3555,19 +3555,19 @@
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD30">
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF30">
         <v>5</v>
@@ -3656,22 +3656,22 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3754,25 +3754,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB32">
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3855,25 +3855,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE33">
         <v>10</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3959,22 +3959,22 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4060,7 +4060,7 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>5</v>
@@ -4158,25 +4158,25 @@
         <v>10</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4259,7 +4259,7 @@
         <v>5</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>5</v>
@@ -4268,13 +4268,13 @@
         <v>5</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD37">
         <v>5</v>
       </c>
       <c r="AE37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF37">
         <v>5</v>
@@ -4363,13 +4363,13 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD38">
         <v>5</v>
@@ -4470,13 +4470,13 @@
         <v>5</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD39">
         <v>5</v>
       </c>
       <c r="AE39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF39">
         <v>5</v>
@@ -4562,22 +4562,22 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD40">
         <v>5</v>
       </c>
       <c r="AE40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -7644,7 +7644,7 @@
         <v>51.4</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7676,7 +7676,7 @@
         <v>48.6</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>48.6</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7740,7 +7740,7 @@
         <v>45.9</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7772,7 +7772,7 @@
         <v>27</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7836,7 +7836,7 @@
         <v>21.6</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>16.2</v>
       </c>
       <c r="H9">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="I9">
         <v>0</v>
